--- a/data/database_scheduler.xlsx
+++ b/data/database_scheduler.xlsx
@@ -8,19 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Mersi\BZ\Data Jadwal Pembelajaran\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1C3A23BC-9FBE-44EC-B9E2-92B33F7FC165}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5CEF3EA-DCA3-4824-AFB2-943A0B99BB23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="345" yWindow="30" windowWidth="19560" windowHeight="10890" xr2:uid="{AE6D36E3-81A9-434A-AA02-B2E060EB1A89}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{AE6D36E3-81A9-434A-AA02-B2E060EB1A89}"/>
   </bookViews>
   <sheets>
     <sheet name="Desain" sheetId="1" r:id="rId1"/>
+    <sheet name="Guru" sheetId="2" r:id="rId2"/>
+    <sheet name="Mata Pelajaran" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="162">
   <si>
     <t>No</t>
   </si>
@@ -386,13 +388,133 @@
   </si>
   <si>
     <t>7A,7B,7C,7D,7E,8A,8B</t>
+  </si>
+  <si>
+    <t>ID Guru</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Hari MGMP</t>
+  </si>
+  <si>
+    <t>Prioritas</t>
+  </si>
+  <si>
+    <t>G01</t>
+  </si>
+  <si>
+    <t>PNS</t>
+  </si>
+  <si>
+    <t>G02</t>
+  </si>
+  <si>
+    <t>PPPK</t>
+  </si>
+  <si>
+    <t>G03</t>
+  </si>
+  <si>
+    <t>G04</t>
+  </si>
+  <si>
+    <t>G05</t>
+  </si>
+  <si>
+    <t>G06</t>
+  </si>
+  <si>
+    <t>G07</t>
+  </si>
+  <si>
+    <t>G08</t>
+  </si>
+  <si>
+    <t>G09</t>
+  </si>
+  <si>
+    <t>G10</t>
+  </si>
+  <si>
+    <t>G11</t>
+  </si>
+  <si>
+    <t>G12</t>
+  </si>
+  <si>
+    <t>G13</t>
+  </si>
+  <si>
+    <t>G14</t>
+  </si>
+  <si>
+    <t>G15</t>
+  </si>
+  <si>
+    <t>G16</t>
+  </si>
+  <si>
+    <t>G17</t>
+  </si>
+  <si>
+    <t>G18</t>
+  </si>
+  <si>
+    <t>G19</t>
+  </si>
+  <si>
+    <t>G20</t>
+  </si>
+  <si>
+    <t>G21</t>
+  </si>
+  <si>
+    <t>G22</t>
+  </si>
+  <si>
+    <t>G23</t>
+  </si>
+  <si>
+    <t>G24</t>
+  </si>
+  <si>
+    <t>G25</t>
+  </si>
+  <si>
+    <t>G26</t>
+  </si>
+  <si>
+    <t>G27</t>
+  </si>
+  <si>
+    <t>G28</t>
+  </si>
+  <si>
+    <t>G29</t>
+  </si>
+  <si>
+    <t>G30</t>
+  </si>
+  <si>
+    <t>G31</t>
+  </si>
+  <si>
+    <t>G32</t>
+  </si>
+  <si>
+    <t>G33</t>
+  </si>
+  <si>
+    <t>GTT</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -523,6 +645,12 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -869,8 +997,14 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Aksen1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1228,6 +1362,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3C6ECD3-3DC0-43C1-876A-9C1782668A98}">
   <dimension ref="A1:I34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="14.7109375" customWidth="1"/>
+    <col min="4" max="4" width="21.85546875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
@@ -2215,4 +2353,536 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5B8DE7E-8436-44C6-8ADB-E2F7B7CDD591}">
+  <dimension ref="A1:E36"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.42578125" customWidth="1"/>
+    <col min="2" max="2" width="29.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5703125" customWidth="1"/>
+    <col min="4" max="4" width="13.28515625" customWidth="1"/>
+    <col min="5" max="5" width="11.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B11" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B12" t="s">
+        <v>54</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D12" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B13" t="s">
+        <v>57</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D13" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B14" t="s">
+        <v>59</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D14" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B15" t="s">
+        <v>61</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D15" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B16" t="s">
+        <v>65</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D16" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B17" t="s">
+        <v>71</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D17" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B18" t="s">
+        <v>73</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D18" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B19" t="s">
+        <v>75</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D19" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B20" t="s">
+        <v>77</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D20" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B21" t="s">
+        <v>79</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D21" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B22" t="s">
+        <v>81</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D22" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B23" t="s">
+        <v>85</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D23" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B24" t="s">
+        <v>89</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D24" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B25" t="s">
+        <v>93</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D25" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B26" t="s">
+        <v>96</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D26" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B27" t="s">
+        <v>99</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D27" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B28" t="s">
+        <v>99</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D28" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B29" t="s">
+        <v>104</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D29" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B30" t="s">
+        <v>107</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D30" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B31" t="s">
+        <v>110</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D31" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B32" t="s">
+        <v>112</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D32" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B33" t="s">
+        <v>114</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D33" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B34" t="s">
+        <v>116</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D34" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B35" t="s">
+        <v>120</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D35" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="2"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02E91878-6F62-4424-A587-87E66165FF72}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data/database_scheduler.xlsx
+++ b/data/database_scheduler.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Mersi\BZ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99CFB9B7-9BCA-43A3-A66B-2A76D571E63B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FE39B60-5E12-434D-B1E6-3206BFDBE79A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{AE6D36E3-81A9-434A-AA02-B2E060EB1A89}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{AE6D36E3-81A9-434A-AA02-B2E060EB1A89}"/>
   </bookViews>
   <sheets>
-    <sheet name="Guru" sheetId="2" r:id="rId1"/>
+    <sheet name="Guru_Mengajar" sheetId="2" r:id="rId1"/>
     <sheet name="Mapel" sheetId="3" r:id="rId2"/>
     <sheet name="Rombel" sheetId="7" r:id="rId3"/>
     <sheet name="Prioritas Mapel" sheetId="8" r:id="rId4"/>

--- a/data/database_scheduler.xlsx
+++ b/data/database_scheduler.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Mersi\BZ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCE44581-85F7-4CE9-9487-00899BFDDE13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D94B3E9F-0941-438A-914C-5D731101C495}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{AE6D36E3-81A9-434A-AA02-B2E060EB1A89}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="999" uniqueCount="151">
   <si>
     <t>Nama Guru</t>
   </si>
@@ -32,18 +32,12 @@
     <t>Purwanto, S.Pd.</t>
   </si>
   <si>
-    <t>7A,7B,7C,7D,7E</t>
-  </si>
-  <si>
     <t>Jumat</t>
   </si>
   <si>
     <t>Nurkhasanah, S.Ag.</t>
   </si>
   <si>
-    <t>9A,9B,9C,9D,9E</t>
-  </si>
-  <si>
     <t>Rabu</t>
   </si>
   <si>
@@ -62,27 +56,15 @@
     <t>Rizka Diestriana, S.Pd.</t>
   </si>
   <si>
-    <t>8A,8B,8C,8D,8E</t>
-  </si>
-  <si>
     <t>Anik Mulyani, S.Ag.</t>
   </si>
   <si>
-    <t>7A,7B,7C,7D,7E,8C,8D,8E</t>
-  </si>
-  <si>
     <t>Mersi, S.T.</t>
   </si>
   <si>
-    <t>8A,8B,8C,9A,9B,9C,9D,9E</t>
-  </si>
-  <si>
     <t>Fitri Lestari, S.S.</t>
   </si>
   <si>
-    <t>7A,7B,7C,7D,7E,8A,8B,9A,9B,9C,9D,9E</t>
-  </si>
-  <si>
     <t>Yoma Septiantika, S.Pd.</t>
   </si>
   <si>
@@ -101,15 +83,9 @@
     <t>Cholid Dalyanto, S.Pd.Kor.</t>
   </si>
   <si>
-    <t>7A,7B,7C,8A,8B,8C,8D,8E</t>
-  </si>
-  <si>
     <t>Feni Dwimartanti, S.Pd.</t>
   </si>
   <si>
-    <t>7C,7D,7E,9A,9B,9C,9D,9E</t>
-  </si>
-  <si>
     <t>Senin</t>
   </si>
   <si>
@@ -131,45 +107,27 @@
     <t>Budi Prasetya, S.Pd.</t>
   </si>
   <si>
-    <t>9A,9B,9C,9D,9E,8C,8D,8E</t>
-  </si>
-  <si>
     <t>Iswarasanti, S.Ag.</t>
   </si>
   <si>
-    <t>7A,8C,9A</t>
-  </si>
-  <si>
     <t>Sabti Herma Nugraheni, S.Pd.</t>
   </si>
   <si>
-    <t>7A,8A,9A</t>
-  </si>
-  <si>
     <t>Intan Widiastuti, S.Th.</t>
   </si>
   <si>
     <t>Christina Dwi Ayu Wijaya, S.Pd.</t>
   </si>
   <si>
-    <t>7A,7B,8A,8B,8C,8D,8E</t>
-  </si>
-  <si>
     <t>Thiara Maharani, S.Pd.</t>
   </si>
   <si>
     <t>Luthfan Qaedi Wicaksono, S.Pd.</t>
   </si>
   <si>
-    <t>7D,7E,9A,9B,9C,9D,9E</t>
-  </si>
-  <si>
     <t>Anggiyani Fabilah Parwati, S.Pd.</t>
   </si>
   <si>
-    <t>7A,7B,7C,7D,7E,8D,8E</t>
-  </si>
-  <si>
     <t>Wesda Ayu Rahmadani</t>
   </si>
   <si>
@@ -182,15 +140,9 @@
     <t>Anggi Supriyadi, S.Hum</t>
   </si>
   <si>
-    <t>8A,8B</t>
-  </si>
-  <si>
     <t>Rizal Rahmanto, S.Pd.</t>
   </si>
   <si>
-    <t>7A,7B,7C,7D,7E,8A,8B</t>
-  </si>
-  <si>
     <t>ID Guru</t>
   </si>
   <si>
@@ -308,6 +260,9 @@
     <t>G33</t>
   </si>
   <si>
+    <t>G34</t>
+  </si>
+  <si>
     <t>GTT</t>
   </si>
   <si>
@@ -416,9 +371,6 @@
     <t>Prakarya</t>
   </si>
   <si>
-    <t>Ilmu Penagetahuan Alam</t>
-  </si>
-  <si>
     <t>Kelas</t>
   </si>
   <si>
@@ -518,10 +470,13 @@
     <t>Pembiasaan</t>
   </si>
   <si>
-    <t>8C,8D,8E</t>
-  </si>
-  <si>
     <t>PPPKPW</t>
+  </si>
+  <si>
+    <t>Nurhasanah, S.Ag.</t>
+  </si>
+  <si>
+    <t>Pendidikan Agama Kristen</t>
   </si>
 </sst>
 </file>
@@ -1396,33 +1351,33 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="B2" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="D2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E2" s="1">
         <v>1</v>
@@ -1430,16 +1385,16 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="B3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D3" t="s">
         <v>4</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D3" t="s">
-        <v>6</v>
       </c>
       <c r="E3" s="1">
         <v>2</v>
@@ -1447,16 +1402,16 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="D4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E4" s="1">
         <v>1</v>
@@ -1464,16 +1419,16 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="D5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E5" s="1">
         <v>1</v>
@@ -1481,16 +1436,16 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="D6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
@@ -1498,16 +1453,16 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="D7" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E7" s="1">
         <v>3</v>
@@ -1515,16 +1470,16 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="D8" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E8" s="1">
         <v>2</v>
@@ -1532,16 +1487,16 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="D9" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E9" s="1">
         <v>2</v>
@@ -1549,16 +1504,16 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="D10" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E10" s="1">
         <v>2</v>
@@ -1566,16 +1521,16 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="D11" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E11" s="1">
         <v>2</v>
@@ -1583,16 +1538,16 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="D12" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E12" s="1">
         <v>2</v>
@@ -1600,16 +1555,16 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="B13" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="D13" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E13" s="1">
         <v>2</v>
@@ -1617,16 +1572,16 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="D14" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
@@ -1634,16 +1589,16 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="D15" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E15" s="1">
         <v>1</v>
@@ -1651,16 +1606,16 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="B16" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="D16" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="E16" s="1">
         <v>2</v>
@@ -1668,16 +1623,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="B17" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="D17" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E17" s="1">
         <v>2</v>
@@ -1685,16 +1640,16 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="B18" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="D18" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E18" s="1">
         <v>2</v>
@@ -1702,16 +1657,16 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="B19" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="D19" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E19" s="1">
         <v>1</v>
@@ -1719,16 +1674,16 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="B20" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="D20" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E20" s="1">
         <v>1</v>
@@ -1736,16 +1691,16 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="B21" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="D21" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E21" s="1">
         <v>1</v>
@@ -1753,16 +1708,16 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="B22" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="D22" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E22" s="1">
         <v>2</v>
@@ -1770,16 +1725,16 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="B23" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="D23" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E23" s="1">
         <v>2</v>
@@ -1787,16 +1742,16 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="B24" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="D24" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E24" s="1">
         <v>2</v>
@@ -1804,16 +1759,16 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="B25" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="D25" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E25" s="1">
         <v>2</v>
@@ -1821,16 +1776,16 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="B26" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="D26" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="E26" s="1">
         <v>2</v>
@@ -1838,16 +1793,16 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="B27" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>165</v>
+        <v>148</v>
       </c>
       <c r="D27" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="E27" s="1">
         <v>2</v>
@@ -1855,16 +1810,16 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="B28" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>165</v>
+        <v>148</v>
       </c>
       <c r="D28" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E28" s="1">
         <v>2</v>
@@ -1872,16 +1827,16 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="B29" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>165</v>
+        <v>148</v>
       </c>
       <c r="D29" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E29" s="1">
         <v>1</v>
@@ -1889,16 +1844,16 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="B30" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>165</v>
+        <v>148</v>
       </c>
       <c r="D30" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E30" s="1">
         <v>2</v>
@@ -1906,16 +1861,16 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="B31" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>165</v>
+        <v>148</v>
       </c>
       <c r="D31" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E31" s="1">
         <v>1</v>
@@ -1923,16 +1878,16 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B32" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="D32" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E32" s="1">
         <v>1</v>
@@ -1940,16 +1895,16 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B33" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="D33" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E33" s="1">
         <v>1</v>
@@ -1957,16 +1912,16 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="B34" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="D34" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E34" s="1">
         <v>2</v>
@@ -1974,16 +1929,16 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="B35" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="D35" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E35" s="1">
         <v>2</v>
@@ -2010,21 +1965,21 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="B2" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="C2" s="3">
         <v>3</v>
@@ -2032,10 +1987,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B3" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="C3" s="3">
         <v>3</v>
@@ -2043,10 +1998,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="B4" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="C4" s="3">
         <v>3</v>
@@ -2054,10 +2009,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="B5" t="s">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="C5" s="3">
         <v>3</v>
@@ -2065,10 +2020,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="B6" t="s">
-        <v>123</v>
+        <v>108</v>
       </c>
       <c r="C6" s="3">
         <v>3</v>
@@ -2076,10 +2031,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="B7" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="C7" s="3">
         <v>6</v>
@@ -2087,10 +2042,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="B8" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="C8" s="3">
         <v>4</v>
@@ -2098,10 +2053,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="B9" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="C9" s="3">
         <v>5</v>
@@ -2109,10 +2064,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B10" t="s">
         <v>109</v>
-      </c>
-      <c r="B10" t="s">
-        <v>124</v>
       </c>
       <c r="C10" s="3">
         <v>5</v>
@@ -2120,10 +2075,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B11" t="s">
         <v>110</v>
-      </c>
-      <c r="B11" t="s">
-        <v>125</v>
       </c>
       <c r="C11" s="3">
         <v>4</v>
@@ -2131,10 +2086,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="B12" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="C12" s="3">
         <v>3</v>
@@ -2142,10 +2097,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="B13" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="C13" s="3">
         <v>3</v>
@@ -2153,10 +2108,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="B14" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="C14" s="3">
         <v>3</v>
@@ -2164,10 +2119,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B15" t="s">
         <v>114</v>
-      </c>
-      <c r="B15" t="s">
-        <v>129</v>
       </c>
       <c r="C15" s="3">
         <v>3</v>
@@ -2175,10 +2130,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="B16" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="C16" s="3">
         <v>3</v>
@@ -2186,10 +2141,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="B17" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="C17" s="3">
         <v>1</v>
@@ -2285,18 +2240,18 @@
   <sheetData>
     <row r="1" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>132</v>
+        <v>116</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>133</v>
+        <v>117</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="B2" s="3">
         <v>7</v>
@@ -2305,7 +2260,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="B3" s="3">
         <v>7</v>
@@ -2314,7 +2269,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="B4" s="3">
         <v>7</v>
@@ -2323,7 +2278,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="B5" s="3">
         <v>7</v>
@@ -2332,7 +2287,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>140</v>
+        <v>124</v>
       </c>
       <c r="B6" s="3">
         <v>7</v>
@@ -2340,7 +2295,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="B7" s="3">
         <v>8</v>
@@ -2348,7 +2303,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>141</v>
+        <v>125</v>
       </c>
       <c r="B8" s="3">
         <v>8</v>
@@ -2356,7 +2311,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>142</v>
+        <v>126</v>
       </c>
       <c r="B9" s="3">
         <v>8</v>
@@ -2364,7 +2319,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>143</v>
+        <v>127</v>
       </c>
       <c r="B10" s="3">
         <v>8</v>
@@ -2372,7 +2327,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="B11" s="3">
         <v>8</v>
@@ -2380,7 +2335,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="B12" s="3">
         <v>9</v>
@@ -2388,7 +2343,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>145</v>
+        <v>129</v>
       </c>
       <c r="B13" s="3">
         <v>9</v>
@@ -2396,7 +2351,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="B14" s="3">
         <v>9</v>
@@ -2404,7 +2359,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>147</v>
+        <v>131</v>
       </c>
       <c r="B15" s="3">
         <v>9</v>
@@ -2412,7 +2367,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>148</v>
+        <v>132</v>
       </c>
       <c r="B16" s="3">
         <v>9</v>
@@ -2425,7 +2380,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E6B6589-81EB-464C-9D2E-94A0AC6F84FB}">
-  <dimension ref="A1:L35"/>
+  <dimension ref="A1:L160"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.5703125" customWidth="1"/>
@@ -2438,22 +2393,22 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>149</v>
+        <v>133</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
@@ -2464,22 +2419,22 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="B2" t="s">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>2</v>
+        <v>118</v>
       </c>
       <c r="E2" s="6">
         <v>5</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
@@ -2490,22 +2445,22 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="D3" t="s">
+        <v>119</v>
+      </c>
+      <c r="E3" s="6">
         <v>5</v>
       </c>
-      <c r="E3" s="6">
-        <v>3</v>
-      </c>
-      <c r="F3" s="6">
-        <v>3</v>
+      <c r="F3" s="6" t="s">
+        <v>135</v>
       </c>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
@@ -2516,22 +2471,22 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="D4" t="s">
+        <v>122</v>
+      </c>
+      <c r="E4" s="6">
         <v>5</v>
       </c>
-      <c r="E4" s="6">
-        <v>4</v>
-      </c>
-      <c r="F4" s="6">
-        <v>2.2000000000000002</v>
+      <c r="F4" s="6" t="s">
+        <v>135</v>
       </c>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
@@ -2542,22 +2497,22 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="D5" t="s">
-        <v>5</v>
+        <v>123</v>
       </c>
       <c r="E5" s="6">
         <v>5</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
@@ -2568,22 +2523,22 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="D6" t="s">
-        <v>12</v>
+        <v>124</v>
       </c>
       <c r="E6" s="6">
-        <v>4</v>
-      </c>
-      <c r="F6" s="6">
-        <v>2.2000000000000002</v>
+        <v>5</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>135</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
@@ -2594,16 +2549,16 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>149</v>
       </c>
       <c r="C7" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="D7" t="s">
-        <v>14</v>
+        <v>121</v>
       </c>
       <c r="E7" s="6">
         <v>3</v>
@@ -2620,16 +2575,16 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>149</v>
       </c>
       <c r="C8" t="s">
         <v>103</v>
       </c>
       <c r="D8" t="s">
-        <v>16</v>
+        <v>129</v>
       </c>
       <c r="E8" s="6">
         <v>3</v>
@@ -2640,16 +2595,16 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>149</v>
       </c>
       <c r="C9" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="D9" t="s">
-        <v>18</v>
+        <v>130</v>
       </c>
       <c r="E9" s="6">
         <v>3</v>
@@ -2660,16 +2615,16 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>69</v>
+        <v>45</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>149</v>
       </c>
       <c r="C10" t="s">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="D10" t="s">
-        <v>12</v>
+        <v>131</v>
       </c>
       <c r="E10" s="6">
         <v>3</v>
@@ -2680,236 +2635,236 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>149</v>
       </c>
       <c r="C11" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D11" t="s">
-        <v>5</v>
+        <v>132</v>
       </c>
       <c r="E11" s="6">
-        <v>6</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>152</v>
+        <v>3</v>
+      </c>
+      <c r="F11" s="6">
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C12" t="s">
+        <v>104</v>
+      </c>
+      <c r="D12" t="s">
         <v>121</v>
       </c>
-      <c r="D12" t="s">
-        <v>5</v>
-      </c>
       <c r="E12" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F12" s="6">
-        <v>1</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="B13" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="C13" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="D13" t="s">
-        <v>2</v>
+        <v>129</v>
       </c>
       <c r="E13" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F13" s="6">
-        <v>1</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>73</v>
+        <v>47</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="C14" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D14" t="s">
-        <v>2</v>
+        <v>130</v>
       </c>
       <c r="E14" s="6">
-        <v>6</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>152</v>
+        <v>4</v>
+      </c>
+      <c r="F14" s="6">
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>74</v>
+        <v>47</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="C15" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="D15" t="s">
-        <v>25</v>
+        <v>131</v>
       </c>
       <c r="E15" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F15" s="6">
-        <v>3</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="B16" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="C16" t="s">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="D16" t="s">
-        <v>27</v>
+        <v>132</v>
       </c>
       <c r="E16" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F16" s="6">
-        <v>2.1</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>76</v>
+        <v>48</v>
       </c>
       <c r="B17" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="C17" t="s">
+        <v>84</v>
+      </c>
+      <c r="D17" t="s">
         <v>121</v>
       </c>
-      <c r="D17" t="s">
-        <v>12</v>
-      </c>
       <c r="E17" s="6">
-        <v>1</v>
-      </c>
-      <c r="F17" s="6">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="B18" t="s">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="C18" t="s">
-        <v>120</v>
+        <v>84</v>
       </c>
       <c r="D18" t="s">
+        <v>129</v>
+      </c>
+      <c r="E18" s="6">
         <v>5</v>
       </c>
-      <c r="E18" s="6">
-        <v>3</v>
-      </c>
-      <c r="F18" s="6">
-        <v>3</v>
+      <c r="F18" s="6" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="B19" t="s">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="C19" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="D19" t="s">
-        <v>12</v>
+        <v>130</v>
       </c>
       <c r="E19" s="6">
         <v>5</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>151</v>
+        <v>135</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="B20" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="C20" t="s">
-        <v>124</v>
+        <v>84</v>
       </c>
       <c r="D20" t="s">
-        <v>5</v>
+        <v>131</v>
       </c>
       <c r="E20" s="6">
         <v>5</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>151</v>
+        <v>135</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="B21" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="C21" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="D21" t="s">
-        <v>2</v>
+        <v>132</v>
       </c>
       <c r="E21" s="6">
         <v>5</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>151</v>
+        <v>135</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="B22" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C22" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="D22" t="s">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="E22" s="6">
         <v>4</v>
@@ -2920,96 +2875,96 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>82</v>
+        <v>49</v>
       </c>
       <c r="B23" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="C23" t="s">
-        <v>126</v>
+        <v>104</v>
       </c>
       <c r="D23" t="s">
-        <v>37</v>
+        <v>125</v>
       </c>
       <c r="E23" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F23" s="6">
-        <v>3</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>83</v>
+        <v>49</v>
       </c>
       <c r="B24" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="C24" t="s">
-        <v>127</v>
+        <v>104</v>
       </c>
       <c r="D24" t="s">
-        <v>39</v>
+        <v>126</v>
       </c>
       <c r="E24" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F24" s="6">
-        <v>3</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>84</v>
+        <v>49</v>
       </c>
       <c r="B25" t="s">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="C25" t="s">
-        <v>128</v>
+        <v>104</v>
       </c>
       <c r="D25" t="s">
-        <v>39</v>
+        <v>127</v>
       </c>
       <c r="E25" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F25" s="6">
-        <v>3</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="B26" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="C26" t="s">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="D26" t="s">
-        <v>42</v>
+        <v>128</v>
       </c>
       <c r="E26" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F26" s="6">
-        <v>2.1</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="B27" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="C27" t="s">
-        <v>129</v>
+        <v>103</v>
       </c>
       <c r="D27" t="s">
-        <v>2</v>
+        <v>118</v>
       </c>
       <c r="E27" s="6">
         <v>3</v>
@@ -3020,16 +2975,16 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="B28" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="C28" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="D28" t="s">
-        <v>164</v>
+        <v>119</v>
       </c>
       <c r="E28" s="6">
         <v>3</v>
@@ -3040,16 +2995,16 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>87</v>
+        <v>50</v>
       </c>
       <c r="B29" t="s">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="C29" t="s">
+        <v>103</v>
+      </c>
+      <c r="D29" t="s">
         <v>122</v>
-      </c>
-      <c r="D29" t="s">
-        <v>45</v>
       </c>
       <c r="E29" s="6">
         <v>3</v>
@@ -3060,16 +3015,16 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>88</v>
+        <v>50</v>
       </c>
       <c r="B30" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="C30" t="s">
         <v>103</v>
       </c>
       <c r="D30" t="s">
-        <v>47</v>
+        <v>123</v>
       </c>
       <c r="E30" s="6">
         <v>3</v>
@@ -3080,76 +3035,76 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>89</v>
+        <v>50</v>
       </c>
       <c r="B31" t="s">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="C31" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="D31" t="s">
-        <v>2</v>
+        <v>124</v>
       </c>
       <c r="E31" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F31" s="6">
-        <v>2.2000000000000002</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>90</v>
+        <v>51</v>
       </c>
       <c r="B32" t="s">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="C32" t="s">
-        <v>130</v>
+        <v>88</v>
       </c>
       <c r="D32" t="s">
-        <v>12</v>
+        <v>120</v>
       </c>
       <c r="E32" s="6">
-        <v>5</v>
-      </c>
-      <c r="F32" s="6" t="s">
-        <v>151</v>
+        <v>3</v>
+      </c>
+      <c r="F32" s="6">
+        <v>3</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>91</v>
+        <v>51</v>
       </c>
       <c r="B33" t="s">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="C33" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="D33" t="s">
-        <v>12</v>
+        <v>125</v>
       </c>
       <c r="E33" s="6">
-        <v>6</v>
-      </c>
-      <c r="F33" s="6" t="s">
-        <v>152</v>
+        <v>3</v>
+      </c>
+      <c r="F33" s="6">
+        <v>3</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>92</v>
+        <v>51</v>
       </c>
       <c r="B34" t="s">
-        <v>51</v>
+        <v>11</v>
       </c>
       <c r="C34" t="s">
-        <v>118</v>
+        <v>88</v>
       </c>
       <c r="D34" t="s">
-        <v>52</v>
+        <v>126</v>
       </c>
       <c r="E34" s="6">
         <v>3</v>
@@ -3160,21 +3115,2521 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>93</v>
+        <v>51</v>
       </c>
       <c r="B35" t="s">
+        <v>11</v>
+      </c>
+      <c r="C35" t="s">
+        <v>88</v>
+      </c>
+      <c r="D35" t="s">
+        <v>121</v>
+      </c>
+      <c r="E35" s="6">
+        <v>3</v>
+      </c>
+      <c r="F35" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B36" t="s">
+        <v>11</v>
+      </c>
+      <c r="C36" t="s">
+        <v>88</v>
+      </c>
+      <c r="D36" t="s">
+        <v>129</v>
+      </c>
+      <c r="E36" s="6">
+        <v>3</v>
+      </c>
+      <c r="F36" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B37" t="s">
+        <v>12</v>
+      </c>
+      <c r="C37" t="s">
+        <v>102</v>
+      </c>
+      <c r="D37" t="s">
+        <v>118</v>
+      </c>
+      <c r="E37" s="6">
+        <v>3</v>
+      </c>
+      <c r="F37" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B38" t="s">
+        <v>12</v>
+      </c>
+      <c r="C38" t="s">
+        <v>102</v>
+      </c>
+      <c r="D38" t="s">
+        <v>119</v>
+      </c>
+      <c r="E38" s="6">
+        <v>3</v>
+      </c>
+      <c r="F38" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B39" t="s">
+        <v>12</v>
+      </c>
+      <c r="C39" t="s">
+        <v>102</v>
+      </c>
+      <c r="D39" t="s">
+        <v>122</v>
+      </c>
+      <c r="E39" s="6">
+        <v>3</v>
+      </c>
+      <c r="F39" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B40" t="s">
+        <v>12</v>
+      </c>
+      <c r="C40" t="s">
+        <v>102</v>
+      </c>
+      <c r="D40" t="s">
+        <v>123</v>
+      </c>
+      <c r="E40" s="6">
+        <v>3</v>
+      </c>
+      <c r="F40" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B41" t="s">
+        <v>12</v>
+      </c>
+      <c r="C41" t="s">
+        <v>102</v>
+      </c>
+      <c r="D41" t="s">
+        <v>124</v>
+      </c>
+      <c r="E41" s="6">
+        <v>3</v>
+      </c>
+      <c r="F41" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C35" t="s">
+      <c r="B42" t="s">
+        <v>13</v>
+      </c>
+      <c r="C42" t="s">
+        <v>105</v>
+      </c>
+      <c r="D42" t="s">
+        <v>120</v>
+      </c>
+      <c r="E42" s="6">
+        <v>3</v>
+      </c>
+      <c r="F42" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B43" t="s">
+        <v>13</v>
+      </c>
+      <c r="C43" t="s">
+        <v>105</v>
+      </c>
+      <c r="D43" t="s">
         <v>125</v>
       </c>
-      <c r="D35" t="s">
+      <c r="E43" s="6">
+        <v>3</v>
+      </c>
+      <c r="F43" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B44" t="s">
+        <v>13</v>
+      </c>
+      <c r="C44" t="s">
+        <v>105</v>
+      </c>
+      <c r="D44" t="s">
+        <v>126</v>
+      </c>
+      <c r="E44" s="6">
+        <v>3</v>
+      </c>
+      <c r="F44" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B45" t="s">
+        <v>13</v>
+      </c>
+      <c r="C45" t="s">
+        <v>105</v>
+      </c>
+      <c r="D45" t="s">
+        <v>127</v>
+      </c>
+      <c r="E45" s="6">
+        <v>3</v>
+      </c>
+      <c r="F45" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B46" t="s">
+        <v>13</v>
+      </c>
+      <c r="C46" t="s">
+        <v>105</v>
+      </c>
+      <c r="D46" t="s">
+        <v>128</v>
+      </c>
+      <c r="E46" s="6">
+        <v>3</v>
+      </c>
+      <c r="F46" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="E35" s="6">
+      <c r="B47" t="s">
+        <v>14</v>
+      </c>
+      <c r="C47" t="s">
+        <v>86</v>
+      </c>
+      <c r="D47" t="s">
+        <v>121</v>
+      </c>
+      <c r="E47" s="6">
+        <v>6</v>
+      </c>
+      <c r="F47" s="6" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B48" t="s">
+        <v>14</v>
+      </c>
+      <c r="C48" t="s">
+        <v>86</v>
+      </c>
+      <c r="D48" t="s">
+        <v>129</v>
+      </c>
+      <c r="E48" s="6">
+        <v>6</v>
+      </c>
+      <c r="F48" s="6" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B49" t="s">
+        <v>14</v>
+      </c>
+      <c r="C49" t="s">
+        <v>86</v>
+      </c>
+      <c r="D49" t="s">
+        <v>130</v>
+      </c>
+      <c r="E49" s="6">
+        <v>6</v>
+      </c>
+      <c r="F49" s="6" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B50" t="s">
+        <v>14</v>
+      </c>
+      <c r="C50" t="s">
+        <v>86</v>
+      </c>
+      <c r="D50" t="s">
+        <v>131</v>
+      </c>
+      <c r="E50" s="6">
+        <v>6</v>
+      </c>
+      <c r="F50" s="6" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B51" t="s">
+        <v>14</v>
+      </c>
+      <c r="C51" t="s">
+        <v>86</v>
+      </c>
+      <c r="D51" t="s">
+        <v>132</v>
+      </c>
+      <c r="E51" s="6">
+        <v>6</v>
+      </c>
+      <c r="F51" s="6" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B52" t="s">
+        <v>15</v>
+      </c>
+      <c r="C52" t="s">
+        <v>106</v>
+      </c>
+      <c r="D52" t="s">
+        <v>121</v>
+      </c>
+      <c r="E52" s="6">
+        <v>1</v>
+      </c>
+      <c r="F52" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B53" t="s">
+        <v>15</v>
+      </c>
+      <c r="C53" t="s">
+        <v>106</v>
+      </c>
+      <c r="D53" t="s">
+        <v>129</v>
+      </c>
+      <c r="E53" s="6">
+        <v>1</v>
+      </c>
+      <c r="F53" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B54" t="s">
+        <v>15</v>
+      </c>
+      <c r="C54" t="s">
+        <v>106</v>
+      </c>
+      <c r="D54" t="s">
+        <v>130</v>
+      </c>
+      <c r="E54" s="6">
+        <v>1</v>
+      </c>
+      <c r="F54" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B55" t="s">
+        <v>15</v>
+      </c>
+      <c r="C55" t="s">
+        <v>106</v>
+      </c>
+      <c r="D55" t="s">
+        <v>131</v>
+      </c>
+      <c r="E55" s="6">
+        <v>1</v>
+      </c>
+      <c r="F55" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B56" t="s">
+        <v>15</v>
+      </c>
+      <c r="C56" t="s">
+        <v>106</v>
+      </c>
+      <c r="D56" t="s">
+        <v>132</v>
+      </c>
+      <c r="E56" s="6">
+        <v>1</v>
+      </c>
+      <c r="F56" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B57" t="s">
+        <v>16</v>
+      </c>
+      <c r="C57" t="s">
+        <v>106</v>
+      </c>
+      <c r="D57" t="s">
+        <v>118</v>
+      </c>
+      <c r="E57" s="6">
+        <v>1</v>
+      </c>
+      <c r="F57" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B58" t="s">
+        <v>16</v>
+      </c>
+      <c r="C58" t="s">
+        <v>106</v>
+      </c>
+      <c r="D58" t="s">
+        <v>119</v>
+      </c>
+      <c r="E58" s="6">
+        <v>1</v>
+      </c>
+      <c r="F58" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B59" t="s">
+        <v>16</v>
+      </c>
+      <c r="C59" t="s">
+        <v>106</v>
+      </c>
+      <c r="D59" t="s">
+        <v>122</v>
+      </c>
+      <c r="E59" s="6">
+        <v>1</v>
+      </c>
+      <c r="F59" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B60" t="s">
+        <v>16</v>
+      </c>
+      <c r="C60" t="s">
+        <v>106</v>
+      </c>
+      <c r="D60" t="s">
+        <v>123</v>
+      </c>
+      <c r="E60" s="6">
+        <v>1</v>
+      </c>
+      <c r="F60" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B61" t="s">
+        <v>16</v>
+      </c>
+      <c r="C61" t="s">
+        <v>106</v>
+      </c>
+      <c r="D61" t="s">
+        <v>124</v>
+      </c>
+      <c r="E61" s="6">
+        <v>1</v>
+      </c>
+      <c r="F61" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B62" t="s">
+        <v>17</v>
+      </c>
+      <c r="C62" t="s">
+        <v>86</v>
+      </c>
+      <c r="D62" t="s">
+        <v>118</v>
+      </c>
+      <c r="E62" s="6">
+        <v>6</v>
+      </c>
+      <c r="F62" s="6" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B63" t="s">
+        <v>17</v>
+      </c>
+      <c r="C63" t="s">
+        <v>86</v>
+      </c>
+      <c r="D63" t="s">
+        <v>119</v>
+      </c>
+      <c r="E63" s="6">
+        <v>6</v>
+      </c>
+      <c r="F63" s="6" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B64" t="s">
+        <v>17</v>
+      </c>
+      <c r="C64" t="s">
+        <v>86</v>
+      </c>
+      <c r="D64" t="s">
+        <v>122</v>
+      </c>
+      <c r="E64" s="6">
+        <v>6</v>
+      </c>
+      <c r="F64" s="6" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B65" t="s">
+        <v>17</v>
+      </c>
+      <c r="C65" t="s">
+        <v>86</v>
+      </c>
+      <c r="D65" t="s">
+        <v>123</v>
+      </c>
+      <c r="E65" s="6">
+        <v>6</v>
+      </c>
+      <c r="F65" s="6" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B66" t="s">
+        <v>17</v>
+      </c>
+      <c r="C66" t="s">
+        <v>86</v>
+      </c>
+      <c r="D66" t="s">
+        <v>124</v>
+      </c>
+      <c r="E66" s="6">
+        <v>6</v>
+      </c>
+      <c r="F66" s="6" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B67" t="s">
+        <v>18</v>
+      </c>
+      <c r="C67" t="s">
+        <v>107</v>
+      </c>
+      <c r="D67" t="s">
+        <v>118</v>
+      </c>
+      <c r="E67" s="6">
+        <v>3</v>
+      </c>
+      <c r="F67" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B68" t="s">
+        <v>18</v>
+      </c>
+      <c r="C68" t="s">
+        <v>107</v>
+      </c>
+      <c r="D68" t="s">
+        <v>119</v>
+      </c>
+      <c r="E68" s="6">
+        <v>3</v>
+      </c>
+      <c r="F68" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B69" t="s">
+        <v>18</v>
+      </c>
+      <c r="C69" t="s">
+        <v>107</v>
+      </c>
+      <c r="D69" t="s">
+        <v>122</v>
+      </c>
+      <c r="E69" s="6">
+        <v>3</v>
+      </c>
+      <c r="F69" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B70" t="s">
+        <v>18</v>
+      </c>
+      <c r="C70" t="s">
+        <v>107</v>
+      </c>
+      <c r="D70" t="s">
+        <v>120</v>
+      </c>
+      <c r="E70" s="6">
+        <v>3</v>
+      </c>
+      <c r="F70" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B71" t="s">
+        <v>18</v>
+      </c>
+      <c r="C71" t="s">
+        <v>107</v>
+      </c>
+      <c r="D71" t="s">
+        <v>125</v>
+      </c>
+      <c r="E71" s="6">
+        <v>3</v>
+      </c>
+      <c r="F71" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B72" t="s">
+        <v>19</v>
+      </c>
+      <c r="C72" t="s">
+        <v>108</v>
+      </c>
+      <c r="D72" t="s">
+        <v>122</v>
+      </c>
+      <c r="E72" s="6">
+        <v>3</v>
+      </c>
+      <c r="F72" s="6">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B73" t="s">
+        <v>19</v>
+      </c>
+      <c r="C73" t="s">
+        <v>108</v>
+      </c>
+      <c r="D73" t="s">
+        <v>123</v>
+      </c>
+      <c r="E73" s="6">
+        <v>3</v>
+      </c>
+      <c r="F73" s="6">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B74" t="s">
+        <v>19</v>
+      </c>
+      <c r="C74" t="s">
+        <v>108</v>
+      </c>
+      <c r="D74" t="s">
+        <v>124</v>
+      </c>
+      <c r="E74" s="6">
+        <v>3</v>
+      </c>
+      <c r="F74" s="6">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B75" t="s">
+        <v>19</v>
+      </c>
+      <c r="C75" t="s">
+        <v>108</v>
+      </c>
+      <c r="D75" t="s">
+        <v>121</v>
+      </c>
+      <c r="E75" s="6">
+        <v>3</v>
+      </c>
+      <c r="F75" s="6">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B76" t="s">
+        <v>19</v>
+      </c>
+      <c r="C76" t="s">
+        <v>108</v>
+      </c>
+      <c r="D76" t="s">
+        <v>129</v>
+      </c>
+      <c r="E76" s="6">
+        <v>3</v>
+      </c>
+      <c r="F76" s="6">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B77" t="s">
+        <v>21</v>
+      </c>
+      <c r="C77" t="s">
+        <v>106</v>
+      </c>
+      <c r="D77" t="s">
+        <v>120</v>
+      </c>
+      <c r="E77" s="6">
+        <v>1</v>
+      </c>
+      <c r="F77" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B78" t="s">
+        <v>21</v>
+      </c>
+      <c r="C78" t="s">
+        <v>106</v>
+      </c>
+      <c r="D78" t="s">
+        <v>125</v>
+      </c>
+      <c r="E78" s="6">
+        <v>1</v>
+      </c>
+      <c r="F78" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A79" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B79" t="s">
+        <v>21</v>
+      </c>
+      <c r="C79" t="s">
+        <v>106</v>
+      </c>
+      <c r="D79" t="s">
+        <v>126</v>
+      </c>
+      <c r="E79" s="6">
+        <v>1</v>
+      </c>
+      <c r="F79" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B80" t="s">
+        <v>21</v>
+      </c>
+      <c r="C80" t="s">
+        <v>106</v>
+      </c>
+      <c r="D80" t="s">
+        <v>127</v>
+      </c>
+      <c r="E80" s="6">
+        <v>1</v>
+      </c>
+      <c r="F80" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A81" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B81" t="s">
+        <v>21</v>
+      </c>
+      <c r="C81" t="s">
+        <v>106</v>
+      </c>
+      <c r="D81" t="s">
+        <v>128</v>
+      </c>
+      <c r="E81" s="6">
+        <v>1</v>
+      </c>
+      <c r="F81" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A82" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B82" t="s">
+        <v>22</v>
+      </c>
+      <c r="C82" t="s">
+        <v>105</v>
+      </c>
+      <c r="D82" t="s">
+        <v>121</v>
+      </c>
+      <c r="E82" s="6">
+        <v>3</v>
+      </c>
+      <c r="F82" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B83" t="s">
+        <v>22</v>
+      </c>
+      <c r="C83" t="s">
+        <v>105</v>
+      </c>
+      <c r="D83" t="s">
+        <v>129</v>
+      </c>
+      <c r="E83" s="6">
+        <v>3</v>
+      </c>
+      <c r="F83" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A84" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B84" t="s">
+        <v>22</v>
+      </c>
+      <c r="C84" t="s">
+        <v>105</v>
+      </c>
+      <c r="D84" t="s">
+        <v>130</v>
+      </c>
+      <c r="E84" s="6">
+        <v>3</v>
+      </c>
+      <c r="F84" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B85" t="s">
+        <v>22</v>
+      </c>
+      <c r="C85" t="s">
+        <v>105</v>
+      </c>
+      <c r="D85" t="s">
+        <v>131</v>
+      </c>
+      <c r="E85" s="6">
+        <v>3</v>
+      </c>
+      <c r="F85" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A86" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B86" t="s">
+        <v>22</v>
+      </c>
+      <c r="C86" t="s">
+        <v>105</v>
+      </c>
+      <c r="D86" t="s">
+        <v>132</v>
+      </c>
+      <c r="E86" s="6">
+        <v>3</v>
+      </c>
+      <c r="F86" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A87" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B87" t="s">
+        <v>23</v>
+      </c>
+      <c r="C87" t="s">
+        <v>84</v>
+      </c>
+      <c r="D87" t="s">
+        <v>120</v>
+      </c>
+      <c r="E87" s="6">
+        <v>5</v>
+      </c>
+      <c r="F87" s="6" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A88" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B88" t="s">
+        <v>23</v>
+      </c>
+      <c r="C88" t="s">
+        <v>84</v>
+      </c>
+      <c r="D88" t="s">
+        <v>125</v>
+      </c>
+      <c r="E88" s="6">
+        <v>5</v>
+      </c>
+      <c r="F88" s="6" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A89" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B89" t="s">
+        <v>23</v>
+      </c>
+      <c r="C89" t="s">
+        <v>84</v>
+      </c>
+      <c r="D89" t="s">
+        <v>126</v>
+      </c>
+      <c r="E89" s="6">
+        <v>5</v>
+      </c>
+      <c r="F89" s="6" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A90" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B90" t="s">
+        <v>23</v>
+      </c>
+      <c r="C90" t="s">
+        <v>84</v>
+      </c>
+      <c r="D90" t="s">
+        <v>127</v>
+      </c>
+      <c r="E90" s="6">
+        <v>5</v>
+      </c>
+      <c r="F90" s="6" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A91" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B91" t="s">
+        <v>23</v>
+      </c>
+      <c r="C91" t="s">
+        <v>84</v>
+      </c>
+      <c r="D91" t="s">
+        <v>128</v>
+      </c>
+      <c r="E91" s="6">
+        <v>5</v>
+      </c>
+      <c r="F91" s="6" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A92" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B92" t="s">
+        <v>24</v>
+      </c>
+      <c r="C92" t="s">
+        <v>109</v>
+      </c>
+      <c r="D92" t="s">
+        <v>121</v>
+      </c>
+      <c r="E92" s="6">
+        <v>5</v>
+      </c>
+      <c r="F92" s="6" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A93" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B93" t="s">
+        <v>24</v>
+      </c>
+      <c r="C93" t="s">
+        <v>109</v>
+      </c>
+      <c r="D93" t="s">
+        <v>129</v>
+      </c>
+      <c r="E93" s="6">
+        <v>5</v>
+      </c>
+      <c r="F93" s="6" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A94" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B94" t="s">
+        <v>24</v>
+      </c>
+      <c r="C94" t="s">
+        <v>109</v>
+      </c>
+      <c r="D94" t="s">
+        <v>130</v>
+      </c>
+      <c r="E94" s="6">
+        <v>5</v>
+      </c>
+      <c r="F94" s="6" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A95" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B95" t="s">
+        <v>24</v>
+      </c>
+      <c r="C95" t="s">
+        <v>109</v>
+      </c>
+      <c r="D95" t="s">
+        <v>131</v>
+      </c>
+      <c r="E95" s="6">
+        <v>5</v>
+      </c>
+      <c r="F95" s="6" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A96" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B96" t="s">
+        <v>24</v>
+      </c>
+      <c r="C96" t="s">
+        <v>109</v>
+      </c>
+      <c r="D96" t="s">
+        <v>132</v>
+      </c>
+      <c r="E96" s="6">
+        <v>5</v>
+      </c>
+      <c r="F96" s="6" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A97" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B97" t="s">
+        <v>25</v>
+      </c>
+      <c r="C97" t="s">
+        <v>84</v>
+      </c>
+      <c r="D97" t="s">
+        <v>118</v>
+      </c>
+      <c r="E97" s="6">
+        <v>5</v>
+      </c>
+      <c r="F97" s="6" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A98" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B98" t="s">
+        <v>25</v>
+      </c>
+      <c r="C98" t="s">
+        <v>84</v>
+      </c>
+      <c r="D98" t="s">
+        <v>119</v>
+      </c>
+      <c r="E98" s="6">
+        <v>5</v>
+      </c>
+      <c r="F98" s="6" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A99" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B99" t="s">
+        <v>25</v>
+      </c>
+      <c r="C99" t="s">
+        <v>84</v>
+      </c>
+      <c r="D99" t="s">
+        <v>122</v>
+      </c>
+      <c r="E99" s="6">
+        <v>5</v>
+      </c>
+      <c r="F99" s="6" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A100" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B100" t="s">
+        <v>25</v>
+      </c>
+      <c r="C100" t="s">
+        <v>84</v>
+      </c>
+      <c r="D100" t="s">
+        <v>123</v>
+      </c>
+      <c r="E100" s="6">
+        <v>5</v>
+      </c>
+      <c r="F100" s="6" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A101" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B101" t="s">
+        <v>25</v>
+      </c>
+      <c r="C101" t="s">
+        <v>84</v>
+      </c>
+      <c r="D101" t="s">
+        <v>124</v>
+      </c>
+      <c r="E101" s="6">
+        <v>5</v>
+      </c>
+      <c r="F101" s="6" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A102" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B102" t="s">
+        <v>26</v>
+      </c>
+      <c r="C102" t="s">
+        <v>110</v>
+      </c>
+      <c r="D102" t="s">
+        <v>121</v>
+      </c>
+      <c r="E102" s="6">
         <v>4</v>
       </c>
-      <c r="F35" s="6">
+      <c r="F102" s="6">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A103" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B103" t="s">
+        <v>26</v>
+      </c>
+      <c r="C103" t="s">
+        <v>110</v>
+      </c>
+      <c r="D103" t="s">
+        <v>129</v>
+      </c>
+      <c r="E103" s="6">
+        <v>4</v>
+      </c>
+      <c r="F103" s="6">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A104" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B104" t="s">
+        <v>26</v>
+      </c>
+      <c r="C104" t="s">
+        <v>110</v>
+      </c>
+      <c r="D104" t="s">
+        <v>130</v>
+      </c>
+      <c r="E104" s="6">
+        <v>4</v>
+      </c>
+      <c r="F104" s="6">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A105" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B105" t="s">
+        <v>26</v>
+      </c>
+      <c r="C105" t="s">
+        <v>110</v>
+      </c>
+      <c r="D105" t="s">
+        <v>131</v>
+      </c>
+      <c r="E105" s="6">
+        <v>4</v>
+      </c>
+      <c r="F105" s="6">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A106" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B106" t="s">
+        <v>26</v>
+      </c>
+      <c r="C106" t="s">
+        <v>110</v>
+      </c>
+      <c r="D106" t="s">
+        <v>132</v>
+      </c>
+      <c r="E106" s="6">
+        <v>4</v>
+      </c>
+      <c r="F106" s="6">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A107" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B107" t="s">
+        <v>27</v>
+      </c>
+      <c r="C107" t="s">
+        <v>111</v>
+      </c>
+      <c r="D107" t="s">
+        <v>118</v>
+      </c>
+      <c r="E107" s="6">
+        <v>3</v>
+      </c>
+      <c r="F107" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A108" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B108" t="s">
+        <v>27</v>
+      </c>
+      <c r="C108" t="s">
+        <v>111</v>
+      </c>
+      <c r="D108" t="s">
+        <v>126</v>
+      </c>
+      <c r="E108" s="6">
+        <v>3</v>
+      </c>
+      <c r="F108" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A109" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B109" t="s">
+        <v>27</v>
+      </c>
+      <c r="C109" t="s">
+        <v>111</v>
+      </c>
+      <c r="D109" t="s">
+        <v>121</v>
+      </c>
+      <c r="E109" s="6">
+        <v>3</v>
+      </c>
+      <c r="F109" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A110" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B110" t="s">
+        <v>28</v>
+      </c>
+      <c r="C110" t="s">
+        <v>112</v>
+      </c>
+      <c r="D110" t="s">
+        <v>118</v>
+      </c>
+      <c r="E110" s="6">
+        <v>3</v>
+      </c>
+      <c r="F110" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A111" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B111" t="s">
+        <v>28</v>
+      </c>
+      <c r="C111" t="s">
+        <v>112</v>
+      </c>
+      <c r="D111" t="s">
+        <v>120</v>
+      </c>
+      <c r="E111" s="6">
+        <v>3</v>
+      </c>
+      <c r="F111" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A112" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B112" t="s">
+        <v>28</v>
+      </c>
+      <c r="C112" t="s">
+        <v>112</v>
+      </c>
+      <c r="D112" t="s">
+        <v>121</v>
+      </c>
+      <c r="E112" s="6">
+        <v>3</v>
+      </c>
+      <c r="F112" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A113" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B113" t="s">
+        <v>29</v>
+      </c>
+      <c r="C113" t="s">
+        <v>150</v>
+      </c>
+      <c r="D113" t="s">
+        <v>118</v>
+      </c>
+      <c r="E113" s="6">
+        <v>3</v>
+      </c>
+      <c r="F113" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A114" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B114" t="s">
+        <v>29</v>
+      </c>
+      <c r="C114" t="s">
+        <v>150</v>
+      </c>
+      <c r="D114" t="s">
+        <v>120</v>
+      </c>
+      <c r="E114" s="6">
+        <v>3</v>
+      </c>
+      <c r="F114" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A115" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B115" t="s">
+        <v>29</v>
+      </c>
+      <c r="C115" t="s">
+        <v>150</v>
+      </c>
+      <c r="D115" t="s">
+        <v>121</v>
+      </c>
+      <c r="E115" s="6">
+        <v>3</v>
+      </c>
+      <c r="F115" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A116" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B116" t="s">
+        <v>30</v>
+      </c>
+      <c r="C116" t="s">
+        <v>108</v>
+      </c>
+      <c r="D116" t="s">
+        <v>118</v>
+      </c>
+      <c r="E116" s="6">
+        <v>3</v>
+      </c>
+      <c r="F116" s="6">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A117" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B117" t="s">
+        <v>30</v>
+      </c>
+      <c r="C117" t="s">
+        <v>108</v>
+      </c>
+      <c r="D117" t="s">
+        <v>119</v>
+      </c>
+      <c r="E117" s="6">
+        <v>3</v>
+      </c>
+      <c r="F117" s="6">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A118" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B118" t="s">
+        <v>30</v>
+      </c>
+      <c r="C118" t="s">
+        <v>108</v>
+      </c>
+      <c r="D118" t="s">
+        <v>120</v>
+      </c>
+      <c r="E118" s="6">
+        <v>3</v>
+      </c>
+      <c r="F118" s="6">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A119" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B119" t="s">
+        <v>30</v>
+      </c>
+      <c r="C119" t="s">
+        <v>108</v>
+      </c>
+      <c r="D119" t="s">
+        <v>125</v>
+      </c>
+      <c r="E119" s="6">
+        <v>3</v>
+      </c>
+      <c r="F119" s="6">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A120" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B120" t="s">
+        <v>30</v>
+      </c>
+      <c r="C120" t="s">
+        <v>108</v>
+      </c>
+      <c r="D120" t="s">
+        <v>126</v>
+      </c>
+      <c r="E120" s="6">
+        <v>3</v>
+      </c>
+      <c r="F120" s="6">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A121" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B121" t="s">
+        <v>31</v>
+      </c>
+      <c r="C121" t="s">
+        <v>114</v>
+      </c>
+      <c r="D121" t="s">
+        <v>118</v>
+      </c>
+      <c r="E121" s="6">
+        <v>3</v>
+      </c>
+      <c r="F121" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A122" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B122" t="s">
+        <v>31</v>
+      </c>
+      <c r="C122" t="s">
+        <v>114</v>
+      </c>
+      <c r="D122" t="s">
+        <v>119</v>
+      </c>
+      <c r="E122" s="6">
+        <v>3</v>
+      </c>
+      <c r="F122" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A123" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B123" t="s">
+        <v>31</v>
+      </c>
+      <c r="C123" t="s">
+        <v>114</v>
+      </c>
+      <c r="D123" t="s">
+        <v>122</v>
+      </c>
+      <c r="E123" s="6">
+        <v>3</v>
+      </c>
+      <c r="F123" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A124" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B124" t="s">
+        <v>31</v>
+      </c>
+      <c r="C124" t="s">
+        <v>114</v>
+      </c>
+      <c r="D124" t="s">
+        <v>123</v>
+      </c>
+      <c r="E124" s="6">
+        <v>3</v>
+      </c>
+      <c r="F124" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A125" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B125" t="s">
+        <v>31</v>
+      </c>
+      <c r="C125" t="s">
+        <v>114</v>
+      </c>
+      <c r="D125" t="s">
+        <v>124</v>
+      </c>
+      <c r="E125" s="6">
+        <v>3</v>
+      </c>
+      <c r="F125" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A126" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B126" t="s">
+        <v>31</v>
+      </c>
+      <c r="C126" t="s">
+        <v>102</v>
+      </c>
+      <c r="D126" t="s">
+        <v>126</v>
+      </c>
+      <c r="E126" s="6">
+        <v>3</v>
+      </c>
+      <c r="F126" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A127" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B127" t="s">
+        <v>31</v>
+      </c>
+      <c r="C127" t="s">
+        <v>102</v>
+      </c>
+      <c r="D127" t="s">
+        <v>127</v>
+      </c>
+      <c r="E127" s="6">
+        <v>3</v>
+      </c>
+      <c r="F127" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A128" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B128" t="s">
+        <v>31</v>
+      </c>
+      <c r="C128" t="s">
+        <v>102</v>
+      </c>
+      <c r="D128" t="s">
+        <v>128</v>
+      </c>
+      <c r="E128" s="6">
+        <v>3</v>
+      </c>
+      <c r="F128" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A129" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B129" t="s">
+        <v>32</v>
+      </c>
+      <c r="C129" t="s">
+        <v>107</v>
+      </c>
+      <c r="D129" t="s">
+        <v>123</v>
+      </c>
+      <c r="E129" s="6">
+        <v>3</v>
+      </c>
+      <c r="F129" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A130" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B130" t="s">
+        <v>32</v>
+      </c>
+      <c r="C130" t="s">
+        <v>107</v>
+      </c>
+      <c r="D130" t="s">
+        <v>124</v>
+      </c>
+      <c r="E130" s="6">
+        <v>3</v>
+      </c>
+      <c r="F130" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A131" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B131" t="s">
+        <v>32</v>
+      </c>
+      <c r="C131" t="s">
+        <v>107</v>
+      </c>
+      <c r="D131" t="s">
+        <v>121</v>
+      </c>
+      <c r="E131" s="6">
+        <v>3</v>
+      </c>
+      <c r="F131" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A132" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B132" t="s">
+        <v>32</v>
+      </c>
+      <c r="C132" t="s">
+        <v>107</v>
+      </c>
+      <c r="D132" t="s">
+        <v>129</v>
+      </c>
+      <c r="E132" s="6">
+        <v>3</v>
+      </c>
+      <c r="F132" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A133" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B133" t="s">
+        <v>32</v>
+      </c>
+      <c r="C133" t="s">
+        <v>107</v>
+      </c>
+      <c r="D133" t="s">
+        <v>130</v>
+      </c>
+      <c r="E133" s="6">
+        <v>3</v>
+      </c>
+      <c r="F133" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A134" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B134" t="s">
+        <v>33</v>
+      </c>
+      <c r="C134" t="s">
+        <v>88</v>
+      </c>
+      <c r="D134" t="s">
+        <v>118</v>
+      </c>
+      <c r="E134" s="6">
+        <v>3</v>
+      </c>
+      <c r="F134" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A135" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B135" t="s">
+        <v>33</v>
+      </c>
+      <c r="C135" t="s">
+        <v>88</v>
+      </c>
+      <c r="D135" t="s">
+        <v>119</v>
+      </c>
+      <c r="E135" s="6">
+        <v>3</v>
+      </c>
+      <c r="F135" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A136" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B136" t="s">
+        <v>33</v>
+      </c>
+      <c r="C136" t="s">
+        <v>88</v>
+      </c>
+      <c r="D136" t="s">
+        <v>122</v>
+      </c>
+      <c r="E136" s="6">
+        <v>3</v>
+      </c>
+      <c r="F136" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A137" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B137" t="s">
+        <v>33</v>
+      </c>
+      <c r="C137" t="s">
+        <v>88</v>
+      </c>
+      <c r="D137" t="s">
+        <v>123</v>
+      </c>
+      <c r="E137" s="6">
+        <v>3</v>
+      </c>
+      <c r="F137" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A138" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B138" t="s">
+        <v>33</v>
+      </c>
+      <c r="C138" t="s">
+        <v>88</v>
+      </c>
+      <c r="D138" t="s">
+        <v>124</v>
+      </c>
+      <c r="E138" s="6">
+        <v>3</v>
+      </c>
+      <c r="F138" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A139" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B139" t="s">
+        <v>34</v>
+      </c>
+      <c r="C139" t="s">
+        <v>104</v>
+      </c>
+      <c r="D139" t="s">
+        <v>118</v>
+      </c>
+      <c r="E139" s="6">
+        <v>4</v>
+      </c>
+      <c r="F139" s="6">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A140" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B140" t="s">
+        <v>34</v>
+      </c>
+      <c r="C140" t="s">
+        <v>104</v>
+      </c>
+      <c r="D140" t="s">
+        <v>119</v>
+      </c>
+      <c r="E140" s="6">
+        <v>4</v>
+      </c>
+      <c r="F140" s="6">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A141" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B141" t="s">
+        <v>34</v>
+      </c>
+      <c r="C141" t="s">
+        <v>104</v>
+      </c>
+      <c r="D141" t="s">
+        <v>122</v>
+      </c>
+      <c r="E141" s="6">
+        <v>4</v>
+      </c>
+      <c r="F141" s="6">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A142" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B142" t="s">
+        <v>34</v>
+      </c>
+      <c r="C142" t="s">
+        <v>104</v>
+      </c>
+      <c r="D142" t="s">
+        <v>123</v>
+      </c>
+      <c r="E142" s="6">
+        <v>4</v>
+      </c>
+      <c r="F142" s="6">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A143" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B143" t="s">
+        <v>34</v>
+      </c>
+      <c r="C143" t="s">
+        <v>104</v>
+      </c>
+      <c r="D143" t="s">
+        <v>124</v>
+      </c>
+      <c r="E143" s="6">
+        <v>4</v>
+      </c>
+      <c r="F143" s="6">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A144" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B144" t="s">
+        <v>35</v>
+      </c>
+      <c r="C144" t="s">
+        <v>109</v>
+      </c>
+      <c r="D144" t="s">
+        <v>120</v>
+      </c>
+      <c r="E144" s="6">
+        <v>5</v>
+      </c>
+      <c r="F144" s="6" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A145" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B145" t="s">
+        <v>35</v>
+      </c>
+      <c r="C145" t="s">
+        <v>109</v>
+      </c>
+      <c r="D145" t="s">
+        <v>125</v>
+      </c>
+      <c r="E145" s="6">
+        <v>5</v>
+      </c>
+      <c r="F145" s="6" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A146" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B146" t="s">
+        <v>35</v>
+      </c>
+      <c r="C146" t="s">
+        <v>109</v>
+      </c>
+      <c r="D146" t="s">
+        <v>126</v>
+      </c>
+      <c r="E146" s="6">
+        <v>5</v>
+      </c>
+      <c r="F146" s="6" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A147" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B147" t="s">
+        <v>35</v>
+      </c>
+      <c r="C147" t="s">
+        <v>109</v>
+      </c>
+      <c r="D147" t="s">
+        <v>127</v>
+      </c>
+      <c r="E147" s="6">
+        <v>5</v>
+      </c>
+      <c r="F147" s="6" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A148" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B148" t="s">
+        <v>35</v>
+      </c>
+      <c r="C148" t="s">
+        <v>109</v>
+      </c>
+      <c r="D148" t="s">
+        <v>128</v>
+      </c>
+      <c r="E148" s="6">
+        <v>5</v>
+      </c>
+      <c r="F148" s="6" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A149" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B149" t="s">
+        <v>36</v>
+      </c>
+      <c r="C149" t="s">
+        <v>86</v>
+      </c>
+      <c r="D149" t="s">
+        <v>120</v>
+      </c>
+      <c r="E149" s="6">
+        <v>6</v>
+      </c>
+      <c r="F149" s="6" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A150" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B150" t="s">
+        <v>36</v>
+      </c>
+      <c r="C150" t="s">
+        <v>86</v>
+      </c>
+      <c r="D150" t="s">
+        <v>125</v>
+      </c>
+      <c r="E150" s="6">
+        <v>6</v>
+      </c>
+      <c r="F150" s="6" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A151" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B151" t="s">
+        <v>36</v>
+      </c>
+      <c r="C151" t="s">
+        <v>86</v>
+      </c>
+      <c r="D151" t="s">
+        <v>126</v>
+      </c>
+      <c r="E151" s="6">
+        <v>6</v>
+      </c>
+      <c r="F151" s="6" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A152" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B152" t="s">
+        <v>36</v>
+      </c>
+      <c r="C152" t="s">
+        <v>86</v>
+      </c>
+      <c r="D152" t="s">
+        <v>127</v>
+      </c>
+      <c r="E152" s="6">
+        <v>6</v>
+      </c>
+      <c r="F152" s="6" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A153" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B153" t="s">
+        <v>36</v>
+      </c>
+      <c r="C153" t="s">
+        <v>86</v>
+      </c>
+      <c r="D153" t="s">
+        <v>128</v>
+      </c>
+      <c r="E153" s="6">
+        <v>6</v>
+      </c>
+      <c r="F153" s="6" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A154" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B154" t="s">
+        <v>37</v>
+      </c>
+      <c r="C154" t="s">
+        <v>103</v>
+      </c>
+      <c r="D154" t="s">
+        <v>120</v>
+      </c>
+      <c r="E154" s="6">
+        <v>3</v>
+      </c>
+      <c r="F154" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A155" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B155" t="s">
+        <v>37</v>
+      </c>
+      <c r="C155" t="s">
+        <v>103</v>
+      </c>
+      <c r="D155" t="s">
+        <v>125</v>
+      </c>
+      <c r="E155" s="6">
+        <v>3</v>
+      </c>
+      <c r="F155" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A156" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B156" t="s">
+        <v>38</v>
+      </c>
+      <c r="C156" t="s">
+        <v>110</v>
+      </c>
+      <c r="D156" t="s">
+        <v>118</v>
+      </c>
+      <c r="E156" s="6">
+        <v>4</v>
+      </c>
+      <c r="F156" s="6">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A157" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B157" t="s">
+        <v>38</v>
+      </c>
+      <c r="C157" t="s">
+        <v>110</v>
+      </c>
+      <c r="D157" t="s">
+        <v>119</v>
+      </c>
+      <c r="E157" s="6">
+        <v>4</v>
+      </c>
+      <c r="F157" s="6">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A158" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B158" t="s">
+        <v>38</v>
+      </c>
+      <c r="C158" t="s">
+        <v>110</v>
+      </c>
+      <c r="D158" t="s">
+        <v>122</v>
+      </c>
+      <c r="E158" s="6">
+        <v>4</v>
+      </c>
+      <c r="F158" s="6">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A159" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B159" t="s">
+        <v>38</v>
+      </c>
+      <c r="C159" t="s">
+        <v>110</v>
+      </c>
+      <c r="D159" t="s">
+        <v>123</v>
+      </c>
+      <c r="E159" s="6">
+        <v>4</v>
+      </c>
+      <c r="F159" s="6">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A160" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B160" t="s">
+        <v>38</v>
+      </c>
+      <c r="C160" t="s">
+        <v>110</v>
+      </c>
+      <c r="D160" t="s">
+        <v>124</v>
+      </c>
+      <c r="E160" s="6">
+        <v>4</v>
+      </c>
+      <c r="F160" s="6">
         <v>2.2000000000000002</v>
       </c>
     </row>
@@ -3198,27 +5653,27 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>153</v>
+        <v>137</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>154</v>
+        <v>138</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>157</v>
+        <v>141</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>158</v>
+        <v>142</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="B2" s="3">
         <v>0</v>
@@ -3233,12 +5688,12 @@
         <v>20</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>159</v>
+        <v>143</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="B3" s="3">
         <v>1</v>
@@ -3253,12 +5708,12 @@
         <v>20</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>159</v>
+        <v>143</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="B4" s="3">
         <v>2</v>
@@ -3273,12 +5728,12 @@
         <v>40</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -3293,12 +5748,12 @@
         <v>40</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="5">
@@ -3311,12 +5766,12 @@
         <v>20</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>161</v>
+        <v>145</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="B7" s="3">
         <v>4</v>
@@ -3331,12 +5786,12 @@
         <v>40</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="B8" s="3">
         <v>5</v>
@@ -3351,12 +5806,12 @@
         <v>40</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="B9" s="3">
         <v>6</v>
@@ -3371,12 +5826,12 @@
         <v>40</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="C10" s="4">
         <v>0.4861111111111111</v>
@@ -3388,12 +5843,12 @@
         <v>40</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="B11" s="3">
         <v>7</v>
@@ -3408,12 +5863,12 @@
         <v>40</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="B12" s="3">
         <v>8</v>
@@ -3428,12 +5883,12 @@
         <v>40</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="B13" s="3">
         <v>9</v>
@@ -3448,12 +5903,12 @@
         <v>40</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B14" s="3">
         <v>0</v>
@@ -3468,12 +5923,12 @@
         <v>20</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>163</v>
+        <v>147</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B15" s="3">
         <v>1</v>
@@ -3488,12 +5943,12 @@
         <v>40</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B16" s="3">
         <v>2</v>
@@ -3508,12 +5963,12 @@
         <v>40</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B17" s="3">
         <v>3</v>
@@ -3528,12 +5983,12 @@
         <v>40</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="5">
@@ -3546,12 +6001,12 @@
         <v>20</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>161</v>
+        <v>145</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B19" s="3">
         <v>4</v>
@@ -3566,12 +6021,12 @@
         <v>40</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B20" s="3">
         <v>5</v>
@@ -3586,12 +6041,12 @@
         <v>40</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B21" s="3">
         <v>6</v>
@@ -3606,12 +6061,12 @@
         <v>40</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C22" s="4">
         <v>0.4861111111111111</v>
@@ -3623,12 +6078,12 @@
         <v>40</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B23" s="3">
         <v>7</v>
@@ -3643,12 +6098,12 @@
         <v>40</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B24" s="3">
         <v>8</v>
@@ -3663,12 +6118,12 @@
         <v>40</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B25" s="3">
         <v>9</v>
@@ -3683,12 +6138,12 @@
         <v>40</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B26" s="3">
         <v>0</v>
@@ -3703,12 +6158,12 @@
         <v>20</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>163</v>
+        <v>147</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B27" s="3">
         <v>1</v>
@@ -3723,12 +6178,12 @@
         <v>40</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B28" s="3">
         <v>2</v>
@@ -3743,12 +6198,12 @@
         <v>40</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B29" s="3">
         <v>3</v>
@@ -3763,12 +6218,12 @@
         <v>40</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B30" s="3"/>
       <c r="C30" s="5">
@@ -3781,12 +6236,12 @@
         <v>20</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>161</v>
+        <v>145</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B31" s="3">
         <v>4</v>
@@ -3801,12 +6256,12 @@
         <v>40</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B32" s="3">
         <v>5</v>
@@ -3821,12 +6276,12 @@
         <v>40</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B33" s="3">
         <v>6</v>
@@ -3841,12 +6296,12 @@
         <v>40</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C34" s="4">
         <v>0.4861111111111111</v>
@@ -3858,12 +6313,12 @@
         <v>40</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B35" s="3">
         <v>7</v>
@@ -3878,12 +6333,12 @@
         <v>40</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B36" s="3">
         <v>8</v>
@@ -3898,12 +6353,12 @@
         <v>40</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B37" s="3">
         <v>9</v>
@@ -3918,12 +6373,12 @@
         <v>40</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B38" s="3">
         <v>0</v>
@@ -3938,12 +6393,12 @@
         <v>20</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>163</v>
+        <v>147</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B39" s="3">
         <v>1</v>
@@ -3958,12 +6413,12 @@
         <v>40</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B40" s="3">
         <v>2</v>
@@ -3978,12 +6433,12 @@
         <v>40</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B41" s="3">
         <v>3</v>
@@ -3998,12 +6453,12 @@
         <v>40</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B42" s="3"/>
       <c r="C42" s="5">
@@ -4016,12 +6471,12 @@
         <v>20</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>161</v>
+        <v>145</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B43" s="3">
         <v>4</v>
@@ -4036,12 +6491,12 @@
         <v>40</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B44" s="3">
         <v>5</v>
@@ -4056,12 +6511,12 @@
         <v>40</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B45" s="3">
         <v>6</v>
@@ -4076,12 +6531,12 @@
         <v>40</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C46" s="4">
         <v>0.4861111111111111</v>
@@ -4093,12 +6548,12 @@
         <v>40</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B47" s="3">
         <v>7</v>
@@ -4113,12 +6568,12 @@
         <v>40</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B48" s="3">
         <v>8</v>
@@ -4133,12 +6588,12 @@
         <v>40</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B49" s="3">
         <v>9</v>
@@ -4153,12 +6608,12 @@
         <v>40</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B50" s="3">
         <v>0</v>
@@ -4173,12 +6628,12 @@
         <v>40</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>163</v>
+        <v>147</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B51" s="3">
         <v>1</v>
@@ -4193,12 +6648,12 @@
         <v>30</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B52" s="3">
         <v>2</v>
@@ -4213,12 +6668,12 @@
         <v>30</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B53" s="3">
         <v>3</v>
@@ -4233,12 +6688,12 @@
         <v>30</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B54" s="3"/>
       <c r="C54" s="5">
@@ -4251,12 +6706,12 @@
         <v>20</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>161</v>
+        <v>145</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B55" s="3">
         <v>4</v>
@@ -4271,12 +6726,12 @@
         <v>30</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B56" s="3">
         <v>5</v>
@@ -4291,12 +6746,12 @@
         <v>30</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B57" s="3">
         <v>6</v>
@@ -4311,7 +6766,7 @@
         <v>30</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>

--- a/data/database_scheduler.xlsx
+++ b/data/database_scheduler.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Mersi\BZ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D94B3E9F-0941-438A-914C-5D731101C495}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC449A0F-6230-4998-A4D4-432B0A8C3C6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{AE6D36E3-81A9-434A-AA02-B2E060EB1A89}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="999" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1011" uniqueCount="151">
   <si>
     <t>Nama Guru</t>
   </si>
@@ -2380,7 +2380,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E6B6589-81EB-464C-9D2E-94A0AC6F84FB}">
-  <dimension ref="A1:L160"/>
+  <dimension ref="A1:L163"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.5703125" customWidth="1"/>
@@ -3095,7 +3095,7 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B34" t="s">
         <v>11</v>
@@ -3115,7 +3115,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B35" t="s">
         <v>11</v>
@@ -3135,7 +3135,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B36" t="s">
         <v>11</v>
@@ -3155,16 +3155,16 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B37" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C37" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="D37" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="E37" s="6">
         <v>3</v>
@@ -3175,16 +3175,16 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B38" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C38" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="D38" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="E38" s="6">
         <v>3</v>
@@ -3195,16 +3195,16 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B39" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C39" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="D39" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="E39" s="6">
         <v>3</v>
@@ -3224,7 +3224,7 @@
         <v>102</v>
       </c>
       <c r="D40" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="E40" s="6">
         <v>3</v>
@@ -3244,7 +3244,7 @@
         <v>102</v>
       </c>
       <c r="D41" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="E41" s="6">
         <v>3</v>
@@ -3255,16 +3255,16 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B42" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C42" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D42" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E42" s="6">
         <v>3</v>
@@ -3275,16 +3275,16 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B43" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C43" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D43" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E43" s="6">
         <v>3</v>
@@ -3295,16 +3295,16 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B44" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C44" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D44" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E44" s="6">
         <v>3</v>
@@ -3324,7 +3324,7 @@
         <v>105</v>
       </c>
       <c r="D45" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="E45" s="6">
         <v>3</v>
@@ -3344,7 +3344,7 @@
         <v>105</v>
       </c>
       <c r="D46" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E46" s="6">
         <v>3</v>
@@ -3355,62 +3355,62 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B47" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C47" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="D47" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E47" s="6">
-        <v>6</v>
-      </c>
-      <c r="F47" s="6" t="s">
-        <v>136</v>
+        <v>3</v>
+      </c>
+      <c r="F47" s="6">
+        <v>3</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B48" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C48" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="D48" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E48" s="6">
-        <v>6</v>
-      </c>
-      <c r="F48" s="6" t="s">
-        <v>136</v>
+        <v>3</v>
+      </c>
+      <c r="F48" s="6">
+        <v>3</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B49" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C49" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="D49" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E49" s="6">
-        <v>6</v>
-      </c>
-      <c r="F49" s="6" t="s">
-        <v>136</v>
+        <v>3</v>
+      </c>
+      <c r="F49" s="6">
+        <v>3</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -3424,7 +3424,7 @@
         <v>86</v>
       </c>
       <c r="D50" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="E50" s="6">
         <v>6</v>
@@ -3444,7 +3444,7 @@
         <v>86</v>
       </c>
       <c r="D51" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E51" s="6">
         <v>6</v>
@@ -3455,62 +3455,62 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B52" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C52" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="D52" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="E52" s="6">
-        <v>1</v>
-      </c>
-      <c r="F52" s="6">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="F52" s="6" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C53" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="D53" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E53" s="6">
-        <v>1</v>
-      </c>
-      <c r="F53" s="6">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="F53" s="6" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B54" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C54" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="D54" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E54" s="6">
-        <v>1</v>
-      </c>
-      <c r="F54" s="6">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="F54" s="6" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -3524,7 +3524,7 @@
         <v>106</v>
       </c>
       <c r="D55" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="E55" s="6">
         <v>1</v>
@@ -3544,7 +3544,7 @@
         <v>106</v>
       </c>
       <c r="D56" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E56" s="6">
         <v>1</v>
@@ -3555,16 +3555,16 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C57" t="s">
         <v>106</v>
       </c>
       <c r="D57" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="E57" s="6">
         <v>1</v>
@@ -3575,16 +3575,16 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B58" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C58" t="s">
         <v>106</v>
       </c>
       <c r="D58" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="E58" s="6">
         <v>1</v>
@@ -3595,16 +3595,16 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B59" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C59" t="s">
         <v>106</v>
       </c>
       <c r="D59" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="E59" s="6">
         <v>1</v>
@@ -3624,7 +3624,7 @@
         <v>106</v>
       </c>
       <c r="D60" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="E60" s="6">
         <v>1</v>
@@ -3644,7 +3644,7 @@
         <v>106</v>
       </c>
       <c r="D61" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="E61" s="6">
         <v>1</v>
@@ -3655,62 +3655,62 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B62" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C62" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="D62" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E62" s="6">
-        <v>6</v>
-      </c>
-      <c r="F62" s="6" t="s">
-        <v>136</v>
+        <v>1</v>
+      </c>
+      <c r="F62" s="6">
+        <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B63" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C63" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="D63" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="E63" s="6">
-        <v>6</v>
-      </c>
-      <c r="F63" s="6" t="s">
-        <v>136</v>
+        <v>1</v>
+      </c>
+      <c r="F63" s="6">
+        <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B64" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C64" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="D64" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E64" s="6">
-        <v>6</v>
-      </c>
-      <c r="F64" s="6" t="s">
-        <v>136</v>
+        <v>1</v>
+      </c>
+      <c r="F64" s="6">
+        <v>1</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -3724,7 +3724,7 @@
         <v>86</v>
       </c>
       <c r="D65" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="E65" s="6">
         <v>6</v>
@@ -3744,7 +3744,7 @@
         <v>86</v>
       </c>
       <c r="D66" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="E66" s="6">
         <v>6</v>
@@ -3755,62 +3755,62 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B67" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C67" t="s">
-        <v>107</v>
+        <v>86</v>
       </c>
       <c r="D67" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E67" s="6">
-        <v>3</v>
-      </c>
-      <c r="F67" s="6">
-        <v>3</v>
+        <v>6</v>
+      </c>
+      <c r="F67" s="6" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B68" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C68" t="s">
-        <v>107</v>
+        <v>86</v>
       </c>
       <c r="D68" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="E68" s="6">
-        <v>3</v>
-      </c>
-      <c r="F68" s="6">
-        <v>3</v>
+        <v>6</v>
+      </c>
+      <c r="F68" s="6" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B69" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C69" t="s">
-        <v>107</v>
+        <v>86</v>
       </c>
       <c r="D69" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E69" s="6">
-        <v>3</v>
-      </c>
-      <c r="F69" s="6">
-        <v>3</v>
+        <v>6</v>
+      </c>
+      <c r="F69" s="6" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -3824,7 +3824,7 @@
         <v>107</v>
       </c>
       <c r="D70" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E70" s="6">
         <v>3</v>
@@ -3844,7 +3844,7 @@
         <v>107</v>
       </c>
       <c r="D71" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="E71" s="6">
         <v>3</v>
@@ -3855,13 +3855,13 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B72" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C72" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D72" t="s">
         <v>122</v>
@@ -3870,47 +3870,47 @@
         <v>3</v>
       </c>
       <c r="F72" s="6">
-        <v>2.1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B73" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C73" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D73" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E73" s="6">
         <v>3</v>
       </c>
       <c r="F73" s="6">
-        <v>2.1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B74" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C74" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D74" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E74" s="6">
         <v>3</v>
       </c>
       <c r="F74" s="6">
-        <v>2.1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -3924,7 +3924,7 @@
         <v>108</v>
       </c>
       <c r="D75" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E75" s="6">
         <v>3</v>
@@ -3944,7 +3944,7 @@
         <v>108</v>
       </c>
       <c r="D76" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="E76" s="6">
         <v>3</v>
@@ -3955,62 +3955,62 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B77" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C77" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D77" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E77" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F77" s="6">
-        <v>1</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B78" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C78" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D78" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="E78" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F78" s="6">
-        <v>1</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B79" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C79" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D79" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E79" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F79" s="6">
-        <v>1</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -4024,7 +4024,7 @@
         <v>106</v>
       </c>
       <c r="D80" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="E80" s="6">
         <v>1</v>
@@ -4044,7 +4044,7 @@
         <v>106</v>
       </c>
       <c r="D81" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E81" s="6">
         <v>1</v>
@@ -4055,62 +4055,62 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B82" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C82" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D82" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E82" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F82" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B83" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C83" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D83" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E83" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F83" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B84" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C84" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D84" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E84" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F84" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -4124,7 +4124,7 @@
         <v>105</v>
       </c>
       <c r="D85" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="E85" s="6">
         <v>3</v>
@@ -4144,7 +4144,7 @@
         <v>105</v>
       </c>
       <c r="D86" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E86" s="6">
         <v>3</v>
@@ -4155,62 +4155,62 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B87" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C87" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="D87" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="E87" s="6">
-        <v>5</v>
-      </c>
-      <c r="F87" s="6" t="s">
-        <v>135</v>
+        <v>3</v>
+      </c>
+      <c r="F87" s="6">
+        <v>3</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B88" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C88" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="D88" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="E88" s="6">
-        <v>5</v>
-      </c>
-      <c r="F88" s="6" t="s">
-        <v>135</v>
+        <v>3</v>
+      </c>
+      <c r="F88" s="6">
+        <v>3</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B89" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C89" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="D89" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="E89" s="6">
-        <v>5</v>
-      </c>
-      <c r="F89" s="6" t="s">
-        <v>135</v>
+        <v>3</v>
+      </c>
+      <c r="F89" s="6">
+        <v>3</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -4224,7 +4224,7 @@
         <v>84</v>
       </c>
       <c r="D90" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="E90" s="6">
         <v>5</v>
@@ -4244,7 +4244,7 @@
         <v>84</v>
       </c>
       <c r="D91" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E91" s="6">
         <v>5</v>
@@ -4255,16 +4255,16 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B92" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C92" t="s">
-        <v>109</v>
+        <v>84</v>
       </c>
       <c r="D92" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E92" s="6">
         <v>5</v>
@@ -4275,16 +4275,16 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B93" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C93" t="s">
-        <v>109</v>
+        <v>84</v>
       </c>
       <c r="D93" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E93" s="6">
         <v>5</v>
@@ -4295,16 +4295,16 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B94" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C94" t="s">
-        <v>109</v>
+        <v>84</v>
       </c>
       <c r="D94" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E94" s="6">
         <v>5</v>
@@ -4324,7 +4324,7 @@
         <v>109</v>
       </c>
       <c r="D95" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="E95" s="6">
         <v>5</v>
@@ -4344,7 +4344,7 @@
         <v>109</v>
       </c>
       <c r="D96" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E96" s="6">
         <v>5</v>
@@ -4355,16 +4355,16 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B97" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C97" t="s">
-        <v>84</v>
+        <v>109</v>
       </c>
       <c r="D97" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="E97" s="6">
         <v>5</v>
@@ -4375,16 +4375,16 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B98" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C98" t="s">
-        <v>84</v>
+        <v>109</v>
       </c>
       <c r="D98" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="E98" s="6">
         <v>5</v>
@@ -4395,16 +4395,16 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B99" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C99" t="s">
-        <v>84</v>
+        <v>109</v>
       </c>
       <c r="D99" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="E99" s="6">
         <v>5</v>
@@ -4424,7 +4424,7 @@
         <v>84</v>
       </c>
       <c r="D100" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="E100" s="6">
         <v>5</v>
@@ -4444,7 +4444,7 @@
         <v>84</v>
       </c>
       <c r="D101" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="E101" s="6">
         <v>5</v>
@@ -4455,62 +4455,62 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B102" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C102" t="s">
-        <v>110</v>
+        <v>84</v>
       </c>
       <c r="D102" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E102" s="6">
-        <v>4</v>
-      </c>
-      <c r="F102" s="6">
-        <v>2.2000000000000002</v>
+        <v>5</v>
+      </c>
+      <c r="F102" s="6" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B103" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C103" t="s">
-        <v>110</v>
+        <v>84</v>
       </c>
       <c r="D103" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="E103" s="6">
-        <v>4</v>
-      </c>
-      <c r="F103" s="6">
-        <v>2.2000000000000002</v>
+        <v>5</v>
+      </c>
+      <c r="F103" s="6" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B104" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C104" t="s">
-        <v>110</v>
+        <v>84</v>
       </c>
       <c r="D104" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="E104" s="6">
-        <v>4</v>
-      </c>
-      <c r="F104" s="6">
-        <v>2.2000000000000002</v>
+        <v>5</v>
+      </c>
+      <c r="F104" s="6" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
@@ -4524,7 +4524,7 @@
         <v>110</v>
       </c>
       <c r="D105" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="E105" s="6">
         <v>4</v>
@@ -4544,7 +4544,7 @@
         <v>110</v>
       </c>
       <c r="D106" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E106" s="6">
         <v>4</v>
@@ -4555,73 +4555,73 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B107" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C107" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D107" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="E107" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F107" s="6">
-        <v>3</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B108" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C108" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D108" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="E108" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F108" s="6">
-        <v>3</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B109" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C109" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D109" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="E109" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F109" s="6">
-        <v>3</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B110" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C110" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D110" t="s">
         <v>118</v>
@@ -4635,16 +4635,16 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B111" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C111" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D111" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="E111" s="6">
         <v>3</v>
@@ -4655,13 +4655,13 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B112" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C112" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D112" t="s">
         <v>121</v>
@@ -4675,13 +4675,13 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B113" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C113" t="s">
-        <v>150</v>
+        <v>112</v>
       </c>
       <c r="D113" t="s">
         <v>118</v>
@@ -4695,13 +4695,13 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B114" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C114" t="s">
-        <v>150</v>
+        <v>112</v>
       </c>
       <c r="D114" t="s">
         <v>120</v>
@@ -4715,13 +4715,13 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B115" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C115" t="s">
-        <v>150</v>
+        <v>112</v>
       </c>
       <c r="D115" t="s">
         <v>121</v>
@@ -4735,13 +4735,13 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B116" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C116" t="s">
-        <v>108</v>
+        <v>150</v>
       </c>
       <c r="D116" t="s">
         <v>118</v>
@@ -4750,47 +4750,47 @@
         <v>3</v>
       </c>
       <c r="F116" s="6">
-        <v>2.1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B117" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C117" t="s">
-        <v>108</v>
+        <v>150</v>
       </c>
       <c r="D117" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E117" s="6">
         <v>3</v>
       </c>
       <c r="F117" s="6">
-        <v>2.1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B118" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C118" t="s">
-        <v>108</v>
+        <v>150</v>
       </c>
       <c r="D118" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E118" s="6">
         <v>3</v>
       </c>
       <c r="F118" s="6">
-        <v>2.1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
@@ -4804,7 +4804,7 @@
         <v>108</v>
       </c>
       <c r="D119" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="E119" s="6">
         <v>3</v>
@@ -4824,7 +4824,7 @@
         <v>108</v>
       </c>
       <c r="D120" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="E120" s="6">
         <v>3</v>
@@ -4835,62 +4835,62 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B121" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C121" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="D121" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E121" s="6">
         <v>3</v>
       </c>
       <c r="F121" s="6">
-        <v>3</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B122" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C122" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="D122" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="E122" s="6">
         <v>3</v>
       </c>
       <c r="F122" s="6">
-        <v>3</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B123" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C123" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="D123" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E123" s="6">
         <v>3</v>
       </c>
       <c r="F123" s="6">
-        <v>3</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -4904,7 +4904,7 @@
         <v>114</v>
       </c>
       <c r="D124" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="E124" s="6">
         <v>3</v>
@@ -4924,7 +4924,7 @@
         <v>114</v>
       </c>
       <c r="D125" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="E125" s="6">
         <v>3</v>
@@ -4941,10 +4941,10 @@
         <v>31</v>
       </c>
       <c r="C126" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="D126" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="E126" s="6">
         <v>3</v>
@@ -4961,10 +4961,10 @@
         <v>31</v>
       </c>
       <c r="C127" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="D127" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E127" s="6">
         <v>3</v>
@@ -4981,10 +4981,10 @@
         <v>31</v>
       </c>
       <c r="C128" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="D128" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="E128" s="6">
         <v>3</v>
@@ -4995,16 +4995,16 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B129" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C129" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="D129" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E129" s="6">
         <v>3</v>
@@ -5015,16 +5015,16 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B130" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C130" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="D130" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E130" s="6">
         <v>3</v>
@@ -5035,16 +5035,16 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B131" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C131" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="D131" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="E131" s="6">
         <v>3</v>
@@ -5064,7 +5064,7 @@
         <v>107</v>
       </c>
       <c r="D132" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="E132" s="6">
         <v>3</v>
@@ -5084,7 +5084,7 @@
         <v>107</v>
       </c>
       <c r="D133" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="E133" s="6">
         <v>3</v>
@@ -5095,16 +5095,16 @@
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B134" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C134" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="D134" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E134" s="6">
         <v>3</v>
@@ -5115,16 +5115,16 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B135" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C135" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="D135" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="E135" s="6">
         <v>3</v>
@@ -5135,16 +5135,16 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B136" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C136" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="D136" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="E136" s="6">
         <v>3</v>
@@ -5164,7 +5164,7 @@
         <v>88</v>
       </c>
       <c r="D137" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="E137" s="6">
         <v>3</v>
@@ -5184,7 +5184,7 @@
         <v>88</v>
       </c>
       <c r="D138" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="E138" s="6">
         <v>3</v>
@@ -5195,62 +5195,62 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B139" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C139" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="D139" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E139" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F139" s="6">
-        <v>2.2000000000000002</v>
+        <v>3</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B140" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C140" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="D140" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="E140" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F140" s="6">
-        <v>2.2000000000000002</v>
+        <v>3</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B141" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C141" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="D141" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E141" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F141" s="6">
-        <v>2.2000000000000002</v>
+        <v>3</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
@@ -5264,7 +5264,7 @@
         <v>104</v>
       </c>
       <c r="D142" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="E142" s="6">
         <v>4</v>
@@ -5284,7 +5284,7 @@
         <v>104</v>
       </c>
       <c r="D143" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="E143" s="6">
         <v>4</v>
@@ -5295,62 +5295,62 @@
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B144" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C144" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="D144" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E144" s="6">
-        <v>5</v>
-      </c>
-      <c r="F144" s="6" t="s">
-        <v>135</v>
+        <v>4</v>
+      </c>
+      <c r="F144" s="6">
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B145" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C145" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="D145" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E145" s="6">
-        <v>5</v>
-      </c>
-      <c r="F145" s="6" t="s">
-        <v>135</v>
+        <v>4</v>
+      </c>
+      <c r="F145" s="6">
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B146" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C146" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="D146" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E146" s="6">
-        <v>5</v>
-      </c>
-      <c r="F146" s="6" t="s">
-        <v>135</v>
+        <v>4</v>
+      </c>
+      <c r="F146" s="6">
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
@@ -5364,7 +5364,7 @@
         <v>109</v>
       </c>
       <c r="D147" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="E147" s="6">
         <v>5</v>
@@ -5384,7 +5384,7 @@
         <v>109</v>
       </c>
       <c r="D148" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E148" s="6">
         <v>5</v>
@@ -5395,62 +5395,62 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B149" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C149" t="s">
-        <v>86</v>
+        <v>109</v>
       </c>
       <c r="D149" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="E149" s="6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F149" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B150" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C150" t="s">
-        <v>86</v>
+        <v>109</v>
       </c>
       <c r="D150" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E150" s="6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F150" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B151" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C151" t="s">
-        <v>86</v>
+        <v>109</v>
       </c>
       <c r="D151" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E151" s="6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F151" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
@@ -5464,7 +5464,7 @@
         <v>86</v>
       </c>
       <c r="D152" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="E152" s="6">
         <v>6</v>
@@ -5484,7 +5484,7 @@
         <v>86</v>
       </c>
       <c r="D153" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E153" s="6">
         <v>6</v>
@@ -5495,102 +5495,102 @@
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B154" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C154" t="s">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="D154" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="E154" s="6">
-        <v>3</v>
-      </c>
-      <c r="F154" s="6">
-        <v>3</v>
+        <v>6</v>
+      </c>
+      <c r="F154" s="6" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B155" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C155" t="s">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="D155" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E155" s="6">
-        <v>3</v>
-      </c>
-      <c r="F155" s="6">
-        <v>3</v>
+        <v>6</v>
+      </c>
+      <c r="F155" s="6" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B156" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C156" t="s">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="D156" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="E156" s="6">
-        <v>4</v>
-      </c>
-      <c r="F156" s="6">
-        <v>2.2000000000000002</v>
+        <v>6</v>
+      </c>
+      <c r="F156" s="6" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B157" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C157" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="D157" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E157" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F157" s="6">
-        <v>2.2000000000000002</v>
+        <v>3</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B158" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C158" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="D158" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="E158" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F158" s="6">
-        <v>2.2000000000000002</v>
+        <v>3</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
@@ -5604,7 +5604,7 @@
         <v>110</v>
       </c>
       <c r="D159" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="E159" s="6">
         <v>4</v>
@@ -5624,12 +5624,72 @@
         <v>110</v>
       </c>
       <c r="D160" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="E160" s="6">
         <v>4</v>
       </c>
       <c r="F160" s="6">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A161" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B161" t="s">
+        <v>38</v>
+      </c>
+      <c r="C161" t="s">
+        <v>110</v>
+      </c>
+      <c r="D161" t="s">
+        <v>122</v>
+      </c>
+      <c r="E161" s="6">
+        <v>4</v>
+      </c>
+      <c r="F161" s="6">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A162" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B162" t="s">
+        <v>38</v>
+      </c>
+      <c r="C162" t="s">
+        <v>110</v>
+      </c>
+      <c r="D162" t="s">
+        <v>123</v>
+      </c>
+      <c r="E162" s="6">
+        <v>4</v>
+      </c>
+      <c r="F162" s="6">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A163" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B163" t="s">
+        <v>38</v>
+      </c>
+      <c r="C163" t="s">
+        <v>110</v>
+      </c>
+      <c r="D163" t="s">
+        <v>124</v>
+      </c>
+      <c r="E163" s="6">
+        <v>4</v>
+      </c>
+      <c r="F163" s="6">
         <v>2.2000000000000002</v>
       </c>
     </row>

--- a/data/database_scheduler.xlsx
+++ b/data/database_scheduler.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Mersi\BZ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC449A0F-6230-4998-A4D4-432B0A8C3C6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{984948D0-8105-4536-8709-A76B84875D03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{AE6D36E3-81A9-434A-AA02-B2E060EB1A89}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1011" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1075" uniqueCount="151">
   <si>
     <t>Nama Guru</t>
   </si>
@@ -2380,7 +2380,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E6B6589-81EB-464C-9D2E-94A0AC6F84FB}">
-  <dimension ref="A1:L163"/>
+  <dimension ref="A1:L179"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.5703125" customWidth="1"/>
@@ -3058,13 +3058,13 @@
         <v>51</v>
       </c>
       <c r="B32" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C32" t="s">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="D32" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="E32" s="6">
         <v>3</v>
@@ -3075,16 +3075,16 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B33" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C33" t="s">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="D33" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E33" s="6">
         <v>3</v>
@@ -3095,16 +3095,16 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B34" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C34" t="s">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="D34" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E34" s="6">
         <v>3</v>
@@ -3115,7 +3115,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B35" t="s">
         <v>11</v>
@@ -3124,7 +3124,7 @@
         <v>88</v>
       </c>
       <c r="D35" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E35" s="6">
         <v>3</v>
@@ -3135,7 +3135,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B36" t="s">
         <v>11</v>
@@ -3144,7 +3144,7 @@
         <v>88</v>
       </c>
       <c r="D36" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E36" s="6">
         <v>3</v>
@@ -3155,7 +3155,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B37" t="s">
         <v>11</v>
@@ -3164,7 +3164,7 @@
         <v>88</v>
       </c>
       <c r="D37" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E37" s="6">
         <v>3</v>
@@ -3175,7 +3175,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B38" t="s">
         <v>11</v>
@@ -3184,7 +3184,7 @@
         <v>88</v>
       </c>
       <c r="D38" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="E38" s="6">
         <v>3</v>
@@ -3195,7 +3195,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B39" t="s">
         <v>11</v>
@@ -3204,7 +3204,7 @@
         <v>88</v>
       </c>
       <c r="D39" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E39" s="6">
         <v>3</v>
@@ -3215,16 +3215,16 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B40" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C40" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="D40" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E40" s="6">
         <v>3</v>
@@ -3235,16 +3235,16 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B41" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C41" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="D41" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="E41" s="6">
         <v>3</v>
@@ -3255,16 +3255,16 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B42" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C42" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="D42" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="E42" s="6">
         <v>3</v>
@@ -3284,7 +3284,7 @@
         <v>102</v>
       </c>
       <c r="D43" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="E43" s="6">
         <v>3</v>
@@ -3304,7 +3304,7 @@
         <v>102</v>
       </c>
       <c r="D44" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="E44" s="6">
         <v>3</v>
@@ -3315,16 +3315,16 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B45" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C45" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D45" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E45" s="6">
         <v>3</v>
@@ -3335,16 +3335,16 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B46" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C46" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D46" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E46" s="6">
         <v>3</v>
@@ -3355,16 +3355,16 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B47" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C47" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D47" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E47" s="6">
         <v>3</v>
@@ -3375,16 +3375,16 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B48" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C48" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D48" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="E48" s="6">
         <v>3</v>
@@ -3395,16 +3395,16 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B49" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C49" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D49" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E49" s="6">
         <v>3</v>
@@ -3415,716 +3415,716 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B50" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C50" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="D50" t="s">
         <v>121</v>
       </c>
       <c r="E50" s="6">
-        <v>6</v>
-      </c>
-      <c r="F50" s="6" t="s">
-        <v>136</v>
+        <v>3</v>
+      </c>
+      <c r="F50" s="6">
+        <v>3</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C51" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="D51" t="s">
         <v>129</v>
       </c>
       <c r="E51" s="6">
-        <v>6</v>
-      </c>
-      <c r="F51" s="6" t="s">
-        <v>136</v>
+        <v>3</v>
+      </c>
+      <c r="F51" s="6">
+        <v>3</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B52" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C52" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="D52" t="s">
         <v>130</v>
       </c>
       <c r="E52" s="6">
-        <v>6</v>
-      </c>
-      <c r="F52" s="6" t="s">
-        <v>136</v>
+        <v>3</v>
+      </c>
+      <c r="F52" s="6">
+        <v>3</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C53" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="D53" t="s">
         <v>131</v>
       </c>
       <c r="E53" s="6">
-        <v>6</v>
-      </c>
-      <c r="F53" s="6" t="s">
-        <v>136</v>
+        <v>3</v>
+      </c>
+      <c r="F53" s="6">
+        <v>3</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C54" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="D54" t="s">
         <v>132</v>
       </c>
       <c r="E54" s="6">
-        <v>6</v>
-      </c>
-      <c r="F54" s="6" t="s">
-        <v>136</v>
+        <v>3</v>
+      </c>
+      <c r="F54" s="6">
+        <v>3</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C55" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D55" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E55" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F55" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B56" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C56" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D56" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E56" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F56" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B57" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C57" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D57" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E57" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F57" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B58" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C58" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D58" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E58" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F58" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B59" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C59" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D59" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="E59" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F59" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B60" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C60" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="D60" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E60" s="6">
-        <v>1</v>
-      </c>
-      <c r="F60" s="6">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="F60" s="6" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B61" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C61" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="D61" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="E61" s="6">
-        <v>1</v>
-      </c>
-      <c r="F61" s="6">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="F61" s="6" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B62" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C62" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="D62" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="E62" s="6">
-        <v>1</v>
-      </c>
-      <c r="F62" s="6">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="F62" s="6" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B63" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C63" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="D63" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="E63" s="6">
-        <v>1</v>
-      </c>
-      <c r="F63" s="6">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="F63" s="6" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B64" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C64" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="D64" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="E64" s="6">
-        <v>1</v>
-      </c>
-      <c r="F64" s="6">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="F64" s="6" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B65" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C65" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="D65" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E65" s="6">
-        <v>6</v>
-      </c>
-      <c r="F65" s="6" t="s">
-        <v>136</v>
+        <v>1</v>
+      </c>
+      <c r="F65" s="6">
+        <v>1</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B66" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C66" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="D66" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="E66" s="6">
-        <v>6</v>
-      </c>
-      <c r="F66" s="6" t="s">
-        <v>136</v>
+        <v>1</v>
+      </c>
+      <c r="F66" s="6">
+        <v>1</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B67" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C67" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="D67" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="E67" s="6">
-        <v>6</v>
-      </c>
-      <c r="F67" s="6" t="s">
-        <v>136</v>
+        <v>1</v>
+      </c>
+      <c r="F67" s="6">
+        <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B68" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C68" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="D68" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="E68" s="6">
-        <v>6</v>
-      </c>
-      <c r="F68" s="6" t="s">
-        <v>136</v>
+        <v>1</v>
+      </c>
+      <c r="F68" s="6">
+        <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B69" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C69" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="D69" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="E69" s="6">
-        <v>6</v>
-      </c>
-      <c r="F69" s="6" t="s">
-        <v>136</v>
+        <v>1</v>
+      </c>
+      <c r="F69" s="6">
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B70" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C70" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D70" t="s">
         <v>118</v>
       </c>
       <c r="E70" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F70" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B71" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C71" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D71" t="s">
         <v>119</v>
       </c>
       <c r="E71" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F71" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B72" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C72" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D72" t="s">
         <v>122</v>
       </c>
       <c r="E72" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F72" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B73" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C73" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D73" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E73" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F73" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B74" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C74" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D74" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E74" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F74" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B75" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C75" t="s">
-        <v>108</v>
+        <v>86</v>
       </c>
       <c r="D75" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E75" s="6">
-        <v>3</v>
-      </c>
-      <c r="F75" s="6">
-        <v>2.1</v>
+        <v>6</v>
+      </c>
+      <c r="F75" s="6" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B76" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C76" t="s">
-        <v>108</v>
+        <v>86</v>
       </c>
       <c r="D76" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="E76" s="6">
-        <v>3</v>
-      </c>
-      <c r="F76" s="6">
-        <v>2.1</v>
+        <v>6</v>
+      </c>
+      <c r="F76" s="6" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B77" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C77" t="s">
-        <v>108</v>
+        <v>86</v>
       </c>
       <c r="D77" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E77" s="6">
-        <v>3</v>
-      </c>
-      <c r="F77" s="6">
-        <v>2.1</v>
+        <v>6</v>
+      </c>
+      <c r="F77" s="6" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B78" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C78" t="s">
-        <v>108</v>
+        <v>86</v>
       </c>
       <c r="D78" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E78" s="6">
-        <v>3</v>
-      </c>
-      <c r="F78" s="6">
-        <v>2.1</v>
+        <v>6</v>
+      </c>
+      <c r="F78" s="6" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B79" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C79" t="s">
-        <v>108</v>
+        <v>86</v>
       </c>
       <c r="D79" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="E79" s="6">
-        <v>3</v>
-      </c>
-      <c r="F79" s="6">
-        <v>2.1</v>
+        <v>6</v>
+      </c>
+      <c r="F79" s="6" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B80" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C80" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D80" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E80" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F80" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B81" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C81" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D81" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="E81" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F81" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B82" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C82" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D82" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="E82" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F82" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B83" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C83" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D83" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="E83" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F83" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B84" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C84" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D84" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E84" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F84" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B85" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C85" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D85" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E85" s="6">
         <v>3</v>
@@ -4135,16 +4135,16 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B86" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C86" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D86" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E86" s="6">
         <v>3</v>
@@ -4155,16 +4155,16 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B87" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C87" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D87" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E87" s="6">
         <v>3</v>
@@ -4175,776 +4175,776 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B88" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C88" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D88" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="E88" s="6">
         <v>3</v>
       </c>
       <c r="F88" s="6">
-        <v>3</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B89" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C89" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D89" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="E89" s="6">
         <v>3</v>
       </c>
       <c r="F89" s="6">
-        <v>3</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B90" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C90" t="s">
-        <v>84</v>
+        <v>108</v>
       </c>
       <c r="D90" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E90" s="6">
-        <v>5</v>
-      </c>
-      <c r="F90" s="6" t="s">
-        <v>135</v>
+        <v>3</v>
+      </c>
+      <c r="F90" s="6">
+        <v>2.1</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B91" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C91" t="s">
-        <v>84</v>
+        <v>108</v>
       </c>
       <c r="D91" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="E91" s="6">
-        <v>5</v>
-      </c>
-      <c r="F91" s="6" t="s">
-        <v>135</v>
+        <v>3</v>
+      </c>
+      <c r="F91" s="6">
+        <v>2.1</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B92" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C92" t="s">
-        <v>84</v>
+        <v>108</v>
       </c>
       <c r="D92" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E92" s="6">
-        <v>5</v>
-      </c>
-      <c r="F92" s="6" t="s">
-        <v>135</v>
+        <v>3</v>
+      </c>
+      <c r="F92" s="6">
+        <v>2.1</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B93" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C93" t="s">
-        <v>84</v>
+        <v>108</v>
       </c>
       <c r="D93" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E93" s="6">
-        <v>5</v>
-      </c>
-      <c r="F93" s="6" t="s">
-        <v>135</v>
+        <v>3</v>
+      </c>
+      <c r="F93" s="6">
+        <v>2.1</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B94" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C94" t="s">
-        <v>84</v>
+        <v>108</v>
       </c>
       <c r="D94" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E94" s="6">
-        <v>5</v>
-      </c>
-      <c r="F94" s="6" t="s">
-        <v>135</v>
+        <v>3</v>
+      </c>
+      <c r="F94" s="6">
+        <v>2.1</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B95" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C95" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D95" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="E95" s="6">
-        <v>5</v>
-      </c>
-      <c r="F95" s="6" t="s">
-        <v>135</v>
+        <v>3</v>
+      </c>
+      <c r="F95" s="6">
+        <v>2.1</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B96" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C96" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D96" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="E96" s="6">
-        <v>5</v>
-      </c>
-      <c r="F96" s="6" t="s">
-        <v>135</v>
+        <v>1</v>
+      </c>
+      <c r="F96" s="6">
+        <v>1</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B97" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C97" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D97" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="E97" s="6">
-        <v>5</v>
-      </c>
-      <c r="F97" s="6" t="s">
-        <v>135</v>
+        <v>1</v>
+      </c>
+      <c r="F97" s="6">
+        <v>1</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B98" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C98" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D98" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="E98" s="6">
-        <v>5</v>
-      </c>
-      <c r="F98" s="6" t="s">
-        <v>135</v>
+        <v>1</v>
+      </c>
+      <c r="F98" s="6">
+        <v>1</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B99" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C99" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D99" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="E99" s="6">
-        <v>5</v>
-      </c>
-      <c r="F99" s="6" t="s">
-        <v>135</v>
+        <v>1</v>
+      </c>
+      <c r="F99" s="6">
+        <v>1</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B100" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C100" t="s">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="D100" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="E100" s="6">
-        <v>5</v>
-      </c>
-      <c r="F100" s="6" t="s">
-        <v>135</v>
+        <v>1</v>
+      </c>
+      <c r="F100" s="6">
+        <v>1</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B101" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C101" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="D101" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E101" s="6">
-        <v>5</v>
-      </c>
-      <c r="F101" s="6" t="s">
-        <v>135</v>
+        <v>3</v>
+      </c>
+      <c r="F101" s="6">
+        <v>3</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B102" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C102" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="D102" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="E102" s="6">
-        <v>5</v>
-      </c>
-      <c r="F102" s="6" t="s">
-        <v>135</v>
+        <v>3</v>
+      </c>
+      <c r="F102" s="6">
+        <v>3</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B103" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C103" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="D103" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="E103" s="6">
-        <v>5</v>
-      </c>
-      <c r="F103" s="6" t="s">
-        <v>135</v>
+        <v>3</v>
+      </c>
+      <c r="F103" s="6">
+        <v>3</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B104" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C104" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="D104" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="E104" s="6">
-        <v>5</v>
-      </c>
-      <c r="F104" s="6" t="s">
-        <v>135</v>
+        <v>3</v>
+      </c>
+      <c r="F104" s="6">
+        <v>3</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="3" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B105" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C105" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="D105" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="E105" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F105" s="6">
-        <v>2.2000000000000002</v>
+        <v>3</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B106" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C106" t="s">
-        <v>110</v>
+        <v>84</v>
       </c>
       <c r="D106" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="E106" s="6">
-        <v>4</v>
-      </c>
-      <c r="F106" s="6">
-        <v>2.2000000000000002</v>
+        <v>5</v>
+      </c>
+      <c r="F106" s="6" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B107" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C107" t="s">
-        <v>110</v>
+        <v>84</v>
       </c>
       <c r="D107" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="E107" s="6">
-        <v>4</v>
-      </c>
-      <c r="F107" s="6">
-        <v>2.2000000000000002</v>
+        <v>5</v>
+      </c>
+      <c r="F107" s="6" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="3" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B108" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C108" t="s">
-        <v>110</v>
+        <v>84</v>
       </c>
       <c r="D108" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="E108" s="6">
-        <v>4</v>
-      </c>
-      <c r="F108" s="6">
-        <v>2.2000000000000002</v>
+        <v>5</v>
+      </c>
+      <c r="F108" s="6" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="3" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B109" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C109" t="s">
-        <v>110</v>
+        <v>84</v>
       </c>
       <c r="D109" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="E109" s="6">
-        <v>4</v>
-      </c>
-      <c r="F109" s="6">
-        <v>2.2000000000000002</v>
+        <v>5</v>
+      </c>
+      <c r="F109" s="6" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B110" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C110" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="D110" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="E110" s="6">
-        <v>3</v>
-      </c>
-      <c r="F110" s="6">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="F110" s="6" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="3" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B111" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C111" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D111" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="E111" s="6">
-        <v>3</v>
-      </c>
-      <c r="F111" s="6">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="F111" s="6" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="3" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B112" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C112" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D112" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="E112" s="6">
-        <v>3</v>
-      </c>
-      <c r="F112" s="6">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="F112" s="6" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="3" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B113" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C113" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D113" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="E113" s="6">
-        <v>3</v>
-      </c>
-      <c r="F113" s="6">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="F113" s="6" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="3" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B114" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C114" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D114" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="E114" s="6">
-        <v>3</v>
-      </c>
-      <c r="F114" s="6">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="F114" s="6" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="3" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B115" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C115" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D115" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="E115" s="6">
-        <v>3</v>
-      </c>
-      <c r="F115" s="6">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="F115" s="6" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="3" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="B116" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C116" t="s">
-        <v>150</v>
+        <v>84</v>
       </c>
       <c r="D116" t="s">
         <v>118</v>
       </c>
       <c r="E116" s="6">
-        <v>3</v>
-      </c>
-      <c r="F116" s="6">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="F116" s="6" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="3" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="B117" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C117" t="s">
-        <v>150</v>
+        <v>84</v>
       </c>
       <c r="D117" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E117" s="6">
-        <v>3</v>
-      </c>
-      <c r="F117" s="6">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="F117" s="6" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="3" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="B118" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C118" t="s">
-        <v>150</v>
+        <v>84</v>
       </c>
       <c r="D118" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E118" s="6">
-        <v>3</v>
-      </c>
-      <c r="F118" s="6">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="F118" s="6" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="3" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B119" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C119" t="s">
-        <v>108</v>
+        <v>84</v>
       </c>
       <c r="D119" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="E119" s="6">
-        <v>3</v>
-      </c>
-      <c r="F119" s="6">
-        <v>2.1</v>
+        <v>5</v>
+      </c>
+      <c r="F119" s="6" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="3" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B120" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C120" t="s">
-        <v>108</v>
+        <v>84</v>
       </c>
       <c r="D120" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="E120" s="6">
-        <v>3</v>
-      </c>
-      <c r="F120" s="6">
-        <v>2.1</v>
+        <v>5</v>
+      </c>
+      <c r="F120" s="6" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="3" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B121" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C121" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D121" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E121" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F121" s="6">
-        <v>2.1</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="3" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B122" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C122" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D122" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="E122" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F122" s="6">
-        <v>2.1</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="3" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B123" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C123" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D123" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="E123" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F123" s="6">
-        <v>2.1</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="3" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="B124" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C124" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D124" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="E124" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F124" s="6">
-        <v>3</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="3" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="B125" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C125" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D125" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="E125" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F125" s="6">
-        <v>3</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="3" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="B126" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C126" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D126" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E126" s="6">
         <v>3</v>
@@ -4955,16 +4955,16 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="3" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B127" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C127" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D127" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E127" s="6">
         <v>3</v>
@@ -4975,16 +4975,16 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="3" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B128" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C128" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D128" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E128" s="6">
         <v>3</v>
@@ -4995,16 +4995,16 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="3" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B129" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C129" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="D129" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="E129" s="6">
         <v>3</v>
@@ -5015,16 +5015,16 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="3" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B130" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C130" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="D130" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="E130" s="6">
         <v>3</v>
@@ -5035,16 +5035,16 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="3" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B131" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C131" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="D131" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="E131" s="6">
         <v>3</v>
@@ -5055,16 +5055,16 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B132" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C132" t="s">
-        <v>107</v>
+        <v>150</v>
       </c>
       <c r="D132" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="E132" s="6">
         <v>3</v>
@@ -5075,16 +5075,16 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B133" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C133" t="s">
-        <v>107</v>
+        <v>150</v>
       </c>
       <c r="D133" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="E133" s="6">
         <v>3</v>
@@ -5095,13 +5095,13 @@
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B134" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C134" t="s">
-        <v>107</v>
+        <v>150</v>
       </c>
       <c r="D134" t="s">
         <v>121</v>
@@ -5115,116 +5115,116 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B135" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C135" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D135" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="E135" s="6">
         <v>3</v>
       </c>
       <c r="F135" s="6">
-        <v>3</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B136" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C136" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D136" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="E136" s="6">
         <v>3</v>
       </c>
       <c r="F136" s="6">
-        <v>3</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B137" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C137" t="s">
-        <v>88</v>
+        <v>108</v>
       </c>
       <c r="D137" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E137" s="6">
         <v>3</v>
       </c>
       <c r="F137" s="6">
-        <v>3</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B138" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C138" t="s">
-        <v>88</v>
+        <v>108</v>
       </c>
       <c r="D138" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="E138" s="6">
         <v>3</v>
       </c>
       <c r="F138" s="6">
-        <v>3</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B139" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C139" t="s">
-        <v>88</v>
+        <v>108</v>
       </c>
       <c r="D139" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E139" s="6">
         <v>3</v>
       </c>
       <c r="F139" s="6">
-        <v>3</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B140" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C140" t="s">
-        <v>88</v>
+        <v>114</v>
       </c>
       <c r="D140" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="E140" s="6">
         <v>3</v>
@@ -5235,16 +5235,16 @@
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B141" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C141" t="s">
-        <v>88</v>
+        <v>114</v>
       </c>
       <c r="D141" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="E141" s="6">
         <v>3</v>
@@ -5255,316 +5255,316 @@
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B142" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C142" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="D142" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E142" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F142" s="6">
-        <v>2.2000000000000002</v>
+        <v>3</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B143" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C143" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="D143" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="E143" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F143" s="6">
-        <v>2.2000000000000002</v>
+        <v>3</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B144" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C144" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="D144" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E144" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F144" s="6">
-        <v>2.2000000000000002</v>
+        <v>3</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B145" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C145" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D145" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E145" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F145" s="6">
-        <v>2.2000000000000002</v>
+        <v>3</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B146" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C146" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D146" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E146" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F146" s="6">
-        <v>2.2000000000000002</v>
+        <v>3</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="3" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B147" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C147" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="D147" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="E147" s="6">
-        <v>5</v>
-      </c>
-      <c r="F147" s="6" t="s">
-        <v>135</v>
+        <v>3</v>
+      </c>
+      <c r="F147" s="6">
+        <v>3</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B148" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C148" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D148" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E148" s="6">
-        <v>5</v>
-      </c>
-      <c r="F148" s="6" t="s">
-        <v>135</v>
+        <v>3</v>
+      </c>
+      <c r="F148" s="6">
+        <v>3</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B149" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C149" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D149" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E149" s="6">
-        <v>5</v>
-      </c>
-      <c r="F149" s="6" t="s">
-        <v>135</v>
+        <v>3</v>
+      </c>
+      <c r="F149" s="6">
+        <v>3</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B150" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C150" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D150" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="E150" s="6">
-        <v>5</v>
-      </c>
-      <c r="F150" s="6" t="s">
-        <v>135</v>
+        <v>3</v>
+      </c>
+      <c r="F150" s="6">
+        <v>3</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B151" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C151" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D151" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E151" s="6">
-        <v>5</v>
-      </c>
-      <c r="F151" s="6" t="s">
-        <v>135</v>
+        <v>3</v>
+      </c>
+      <c r="F151" s="6">
+        <v>3</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="3" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B152" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C152" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="D152" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="E152" s="6">
-        <v>6</v>
-      </c>
-      <c r="F152" s="6" t="s">
-        <v>136</v>
+        <v>3</v>
+      </c>
+      <c r="F152" s="6">
+        <v>3</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B153" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C153" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D153" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="E153" s="6">
-        <v>6</v>
-      </c>
-      <c r="F153" s="6" t="s">
-        <v>136</v>
+        <v>3</v>
+      </c>
+      <c r="F153" s="6">
+        <v>3</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B154" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C154" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D154" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="E154" s="6">
-        <v>6</v>
-      </c>
-      <c r="F154" s="6" t="s">
-        <v>136</v>
+        <v>3</v>
+      </c>
+      <c r="F154" s="6">
+        <v>3</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B155" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C155" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D155" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E155" s="6">
-        <v>6</v>
-      </c>
-      <c r="F155" s="6" t="s">
-        <v>136</v>
+        <v>3</v>
+      </c>
+      <c r="F155" s="6">
+        <v>3</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B156" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C156" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D156" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="E156" s="6">
-        <v>6</v>
-      </c>
-      <c r="F156" s="6" t="s">
-        <v>136</v>
+        <v>3</v>
+      </c>
+      <c r="F156" s="6">
+        <v>3</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="3" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B157" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C157" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D157" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E157" s="6">
         <v>3</v>
@@ -5575,36 +5575,36 @@
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B158" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C158" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D158" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="E158" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F158" s="6">
-        <v>3</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="3" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B159" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C159" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="D159" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E159" s="6">
         <v>4</v>
@@ -5615,16 +5615,16 @@
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="3" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B160" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C160" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="D160" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E160" s="6">
         <v>4</v>
@@ -5635,16 +5635,16 @@
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="3" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B161" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C161" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="D161" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E161" s="6">
         <v>4</v>
@@ -5655,16 +5655,16 @@
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="3" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B162" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C162" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="D162" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E162" s="6">
         <v>4</v>
@@ -5675,21 +5675,341 @@
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B163" t="s">
+        <v>35</v>
+      </c>
+      <c r="C163" t="s">
+        <v>109</v>
+      </c>
+      <c r="D163" t="s">
+        <v>120</v>
+      </c>
+      <c r="E163" s="6">
+        <v>5</v>
+      </c>
+      <c r="F163" s="6" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A164" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B164" t="s">
+        <v>35</v>
+      </c>
+      <c r="C164" t="s">
+        <v>109</v>
+      </c>
+      <c r="D164" t="s">
+        <v>125</v>
+      </c>
+      <c r="E164" s="6">
+        <v>5</v>
+      </c>
+      <c r="F164" s="6" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A165" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B165" t="s">
+        <v>35</v>
+      </c>
+      <c r="C165" t="s">
+        <v>109</v>
+      </c>
+      <c r="D165" t="s">
+        <v>126</v>
+      </c>
+      <c r="E165" s="6">
+        <v>5</v>
+      </c>
+      <c r="F165" s="6" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A166" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B166" t="s">
+        <v>35</v>
+      </c>
+      <c r="C166" t="s">
+        <v>109</v>
+      </c>
+      <c r="D166" t="s">
+        <v>127</v>
+      </c>
+      <c r="E166" s="6">
+        <v>5</v>
+      </c>
+      <c r="F166" s="6" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A167" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B167" t="s">
+        <v>35</v>
+      </c>
+      <c r="C167" t="s">
+        <v>109</v>
+      </c>
+      <c r="D167" t="s">
+        <v>128</v>
+      </c>
+      <c r="E167" s="6">
+        <v>5</v>
+      </c>
+      <c r="F167" s="6" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A168" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B168" t="s">
+        <v>36</v>
+      </c>
+      <c r="C168" t="s">
+        <v>86</v>
+      </c>
+      <c r="D168" t="s">
+        <v>120</v>
+      </c>
+      <c r="E168" s="6">
+        <v>6</v>
+      </c>
+      <c r="F168" s="6" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A169" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B169" t="s">
+        <v>36</v>
+      </c>
+      <c r="C169" t="s">
+        <v>86</v>
+      </c>
+      <c r="D169" t="s">
+        <v>125</v>
+      </c>
+      <c r="E169" s="6">
+        <v>6</v>
+      </c>
+      <c r="F169" s="6" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A170" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B170" t="s">
+        <v>36</v>
+      </c>
+      <c r="C170" t="s">
+        <v>86</v>
+      </c>
+      <c r="D170" t="s">
+        <v>126</v>
+      </c>
+      <c r="E170" s="6">
+        <v>6</v>
+      </c>
+      <c r="F170" s="6" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A171" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B171" t="s">
+        <v>36</v>
+      </c>
+      <c r="C171" t="s">
+        <v>86</v>
+      </c>
+      <c r="D171" t="s">
+        <v>127</v>
+      </c>
+      <c r="E171" s="6">
+        <v>6</v>
+      </c>
+      <c r="F171" s="6" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A172" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B172" t="s">
+        <v>36</v>
+      </c>
+      <c r="C172" t="s">
+        <v>86</v>
+      </c>
+      <c r="D172" t="s">
+        <v>128</v>
+      </c>
+      <c r="E172" s="6">
+        <v>6</v>
+      </c>
+      <c r="F172" s="6" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A173" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B173" t="s">
+        <v>37</v>
+      </c>
+      <c r="C173" t="s">
+        <v>103</v>
+      </c>
+      <c r="D173" t="s">
+        <v>120</v>
+      </c>
+      <c r="E173" s="6">
+        <v>3</v>
+      </c>
+      <c r="F173" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A174" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B174" t="s">
+        <v>37</v>
+      </c>
+      <c r="C174" t="s">
+        <v>103</v>
+      </c>
+      <c r="D174" t="s">
+        <v>125</v>
+      </c>
+      <c r="E174" s="6">
+        <v>3</v>
+      </c>
+      <c r="F174" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A175" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B163" t="s">
+      <c r="B175" t="s">
         <v>38</v>
       </c>
-      <c r="C163" t="s">
+      <c r="C175" t="s">
         <v>110</v>
       </c>
-      <c r="D163" t="s">
+      <c r="D175" t="s">
+        <v>118</v>
+      </c>
+      <c r="E175" s="6">
+        <v>4</v>
+      </c>
+      <c r="F175" s="6">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A176" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B176" t="s">
+        <v>38</v>
+      </c>
+      <c r="C176" t="s">
+        <v>110</v>
+      </c>
+      <c r="D176" t="s">
+        <v>119</v>
+      </c>
+      <c r="E176" s="6">
+        <v>4</v>
+      </c>
+      <c r="F176" s="6">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A177" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B177" t="s">
+        <v>38</v>
+      </c>
+      <c r="C177" t="s">
+        <v>110</v>
+      </c>
+      <c r="D177" t="s">
+        <v>122</v>
+      </c>
+      <c r="E177" s="6">
+        <v>4</v>
+      </c>
+      <c r="F177" s="6">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A178" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B178" t="s">
+        <v>38</v>
+      </c>
+      <c r="C178" t="s">
+        <v>110</v>
+      </c>
+      <c r="D178" t="s">
+        <v>123</v>
+      </c>
+      <c r="E178" s="6">
+        <v>4</v>
+      </c>
+      <c r="F178" s="6">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A179" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B179" t="s">
+        <v>38</v>
+      </c>
+      <c r="C179" t="s">
+        <v>110</v>
+      </c>
+      <c r="D179" t="s">
         <v>124</v>
       </c>
-      <c r="E163" s="6">
+      <c r="E179" s="6">
         <v>4</v>
       </c>
-      <c r="F163" s="6">
+      <c r="F179" s="6">
         <v>2.2000000000000002</v>
       </c>
     </row>

--- a/data/database_scheduler.xlsx
+++ b/data/database_scheduler.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Mersi\BZ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{984948D0-8105-4536-8709-A76B84875D03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FE9AB7B-A25D-4D67-91B7-1CE9A235834F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{AE6D36E3-81A9-434A-AA02-B2E060EB1A89}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1075" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1075" uniqueCount="150">
   <si>
     <t>Nama Guru</t>
   </si>
@@ -258,9 +258,6 @@
   </si>
   <si>
     <t>G33</t>
-  </si>
-  <si>
-    <t>G34</t>
   </si>
   <si>
     <t>GTT</t>
@@ -1799,7 +1796,7 @@
         <v>31</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D27" t="s">
         <v>20</v>
@@ -1816,7 +1813,7 @@
         <v>31</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D28" t="s">
         <v>6</v>
@@ -1833,7 +1830,7 @@
         <v>32</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D29" t="s">
         <v>4</v>
@@ -1850,7 +1847,7 @@
         <v>33</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D30" t="s">
         <v>8</v>
@@ -1867,7 +1864,7 @@
         <v>34</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D31" t="s">
         <v>6</v>
@@ -1884,7 +1881,7 @@
         <v>35</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D32" t="s">
         <v>2</v>
@@ -1901,7 +1898,7 @@
         <v>36</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D33" t="s">
         <v>6</v>
@@ -1918,7 +1915,7 @@
         <v>37</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D34" t="s">
         <v>4</v>
@@ -1935,7 +1932,7 @@
         <v>38</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D35" t="s">
         <v>4</v>
@@ -1965,21 +1962,21 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>81</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C2" s="3">
         <v>3</v>
@@ -1987,10 +1984,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C3" s="3">
         <v>3</v>
@@ -1998,10 +1995,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C4" s="3">
         <v>3</v>
@@ -2009,10 +2006,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C5" s="3">
         <v>3</v>
@@ -2020,10 +2017,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C6" s="3">
         <v>3</v>
@@ -2031,10 +2028,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C7" s="3">
         <v>6</v>
@@ -2042,10 +2039,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C8" s="3">
         <v>4</v>
@@ -2053,10 +2050,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C9" s="3">
         <v>5</v>
@@ -2064,10 +2061,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C10" s="3">
         <v>5</v>
@@ -2075,10 +2072,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B11" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C11" s="3">
         <v>4</v>
@@ -2086,10 +2083,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B12" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C12" s="3">
         <v>3</v>
@@ -2097,10 +2094,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B13" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C13" s="3">
         <v>3</v>
@@ -2108,10 +2105,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B14" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C14" s="3">
         <v>3</v>
@@ -2119,10 +2116,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B15" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C15" s="3">
         <v>3</v>
@@ -2130,10 +2127,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B16" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C16" s="3">
         <v>3</v>
@@ -2141,10 +2138,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B17" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C17" s="3">
         <v>1</v>
@@ -2240,18 +2237,18 @@
   <sheetData>
     <row r="1" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>116</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B2" s="3">
         <v>7</v>
@@ -2260,7 +2257,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B3" s="3">
         <v>7</v>
@@ -2269,7 +2266,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B4" s="3">
         <v>7</v>
@@ -2278,7 +2275,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B5" s="3">
         <v>7</v>
@@ -2287,7 +2284,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B6" s="3">
         <v>7</v>
@@ -2295,7 +2292,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B7" s="3">
         <v>8</v>
@@ -2303,7 +2300,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B8" s="3">
         <v>8</v>
@@ -2311,7 +2308,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B9" s="3">
         <v>8</v>
@@ -2319,7 +2316,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B10" s="3">
         <v>8</v>
@@ -2327,7 +2324,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B11" s="3">
         <v>8</v>
@@ -2335,7 +2332,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B12" s="3">
         <v>9</v>
@@ -2343,7 +2340,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B13" s="3">
         <v>9</v>
@@ -2351,7 +2348,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B14" s="3">
         <v>9</v>
@@ -2359,7 +2356,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B15" s="3">
         <v>9</v>
@@ -2367,7 +2364,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B16" s="3">
         <v>9</v>
@@ -2399,16 +2396,16 @@
         <v>0</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>133</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>134</v>
       </c>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
@@ -2425,16 +2422,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E2" s="6">
         <v>5</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
@@ -2451,16 +2448,16 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E3" s="6">
         <v>5</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
@@ -2477,16 +2474,16 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E4" s="6">
         <v>5</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
@@ -2503,16 +2500,16 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E5" s="6">
         <v>5</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
@@ -2529,16 +2526,16 @@
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E6" s="6">
         <v>5</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
@@ -2552,13 +2549,13 @@
         <v>45</v>
       </c>
       <c r="B7" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E7" s="6">
         <v>3</v>
@@ -2578,13 +2575,13 @@
         <v>45</v>
       </c>
       <c r="B8" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E8" s="6">
         <v>3</v>
@@ -2598,13 +2595,13 @@
         <v>45</v>
       </c>
       <c r="B9" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D9" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E9" s="6">
         <v>3</v>
@@ -2618,13 +2615,13 @@
         <v>45</v>
       </c>
       <c r="B10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C10" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D10" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E10" s="6">
         <v>3</v>
@@ -2638,13 +2635,13 @@
         <v>45</v>
       </c>
       <c r="B11" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C11" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D11" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E11" s="6">
         <v>3</v>
@@ -2661,10 +2658,10 @@
         <v>5</v>
       </c>
       <c r="C12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D12" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E12" s="6">
         <v>4</v>
@@ -2681,10 +2678,10 @@
         <v>5</v>
       </c>
       <c r="C13" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D13" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E13" s="6">
         <v>4</v>
@@ -2701,10 +2698,10 @@
         <v>5</v>
       </c>
       <c r="C14" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D14" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E14" s="6">
         <v>4</v>
@@ -2721,10 +2718,10 @@
         <v>5</v>
       </c>
       <c r="C15" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D15" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E15" s="6">
         <v>4</v>
@@ -2741,10 +2738,10 @@
         <v>5</v>
       </c>
       <c r="C16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D16" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E16" s="6">
         <v>4</v>
@@ -2761,16 +2758,16 @@
         <v>7</v>
       </c>
       <c r="C17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D17" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E17" s="6">
         <v>5</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -2781,16 +2778,16 @@
         <v>7</v>
       </c>
       <c r="C18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D18" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E18" s="6">
         <v>5</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -2801,16 +2798,16 @@
         <v>7</v>
       </c>
       <c r="C19" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D19" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E19" s="6">
         <v>5</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -2821,16 +2818,16 @@
         <v>7</v>
       </c>
       <c r="C20" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D20" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E20" s="6">
         <v>5</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -2841,16 +2838,16 @@
         <v>7</v>
       </c>
       <c r="C21" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D21" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E21" s="6">
         <v>5</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -2861,10 +2858,10 @@
         <v>9</v>
       </c>
       <c r="C22" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D22" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E22" s="6">
         <v>4</v>
@@ -2881,10 +2878,10 @@
         <v>9</v>
       </c>
       <c r="C23" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D23" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E23" s="6">
         <v>4</v>
@@ -2901,10 +2898,10 @@
         <v>9</v>
       </c>
       <c r="C24" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D24" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E24" s="6">
         <v>4</v>
@@ -2921,10 +2918,10 @@
         <v>9</v>
       </c>
       <c r="C25" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D25" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E25" s="6">
         <v>4</v>
@@ -2941,10 +2938,10 @@
         <v>9</v>
       </c>
       <c r="C26" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D26" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E26" s="6">
         <v>4</v>
@@ -2961,10 +2958,10 @@
         <v>10</v>
       </c>
       <c r="C27" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D27" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E27" s="6">
         <v>3</v>
@@ -2981,10 +2978,10 @@
         <v>10</v>
       </c>
       <c r="C28" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E28" s="6">
         <v>3</v>
@@ -3001,10 +2998,10 @@
         <v>10</v>
       </c>
       <c r="C29" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D29" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E29" s="6">
         <v>3</v>
@@ -3021,10 +3018,10 @@
         <v>10</v>
       </c>
       <c r="C30" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D30" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E30" s="6">
         <v>3</v>
@@ -3041,10 +3038,10 @@
         <v>10</v>
       </c>
       <c r="C31" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D31" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E31" s="6">
         <v>3</v>
@@ -3055,16 +3052,16 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B32" t="s">
         <v>10</v>
       </c>
       <c r="C32" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D32" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E32" s="6">
         <v>3</v>
@@ -3075,16 +3072,16 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B33" t="s">
         <v>10</v>
       </c>
       <c r="C33" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D33" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E33" s="6">
         <v>3</v>
@@ -3095,16 +3092,16 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B34" t="s">
         <v>10</v>
       </c>
       <c r="C34" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D34" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E34" s="6">
         <v>3</v>
@@ -3121,10 +3118,10 @@
         <v>11</v>
       </c>
       <c r="C35" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D35" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E35" s="6">
         <v>3</v>
@@ -3141,10 +3138,10 @@
         <v>11</v>
       </c>
       <c r="C36" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D36" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E36" s="6">
         <v>3</v>
@@ -3155,16 +3152,16 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B37" t="s">
         <v>11</v>
       </c>
       <c r="C37" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D37" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E37" s="6">
         <v>3</v>
@@ -3175,16 +3172,16 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B38" t="s">
         <v>11</v>
       </c>
       <c r="C38" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D38" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E38" s="6">
         <v>3</v>
@@ -3195,16 +3192,16 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B39" t="s">
         <v>11</v>
       </c>
       <c r="C39" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D39" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E39" s="6">
         <v>3</v>
@@ -3215,16 +3212,16 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B40" t="s">
         <v>11</v>
       </c>
       <c r="C40" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D40" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E40" s="6">
         <v>3</v>
@@ -3241,10 +3238,10 @@
         <v>11</v>
       </c>
       <c r="C41" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D41" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E41" s="6">
         <v>3</v>
@@ -3261,10 +3258,10 @@
         <v>11</v>
       </c>
       <c r="C42" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D42" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E42" s="6">
         <v>3</v>
@@ -3281,10 +3278,10 @@
         <v>12</v>
       </c>
       <c r="C43" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D43" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E43" s="6">
         <v>3</v>
@@ -3301,10 +3298,10 @@
         <v>12</v>
       </c>
       <c r="C44" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D44" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E44" s="6">
         <v>3</v>
@@ -3321,10 +3318,10 @@
         <v>12</v>
       </c>
       <c r="C45" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D45" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E45" s="6">
         <v>3</v>
@@ -3341,10 +3338,10 @@
         <v>12</v>
       </c>
       <c r="C46" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D46" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E46" s="6">
         <v>3</v>
@@ -3361,10 +3358,10 @@
         <v>12</v>
       </c>
       <c r="C47" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D47" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E47" s="6">
         <v>3</v>
@@ -3381,10 +3378,10 @@
         <v>12</v>
       </c>
       <c r="C48" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D48" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E48" s="6">
         <v>3</v>
@@ -3401,10 +3398,10 @@
         <v>12</v>
       </c>
       <c r="C49" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D49" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E49" s="6">
         <v>3</v>
@@ -3421,10 +3418,10 @@
         <v>12</v>
       </c>
       <c r="C50" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D50" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E50" s="6">
         <v>3</v>
@@ -3441,10 +3438,10 @@
         <v>12</v>
       </c>
       <c r="C51" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D51" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E51" s="6">
         <v>3</v>
@@ -3461,10 +3458,10 @@
         <v>12</v>
       </c>
       <c r="C52" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D52" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E52" s="6">
         <v>3</v>
@@ -3481,10 +3478,10 @@
         <v>12</v>
       </c>
       <c r="C53" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D53" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E53" s="6">
         <v>3</v>
@@ -3501,10 +3498,10 @@
         <v>12</v>
       </c>
       <c r="C54" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D54" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E54" s="6">
         <v>3</v>
@@ -3521,10 +3518,10 @@
         <v>13</v>
       </c>
       <c r="C55" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D55" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E55" s="6">
         <v>3</v>
@@ -3541,10 +3538,10 @@
         <v>13</v>
       </c>
       <c r="C56" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D56" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E56" s="6">
         <v>3</v>
@@ -3561,10 +3558,10 @@
         <v>13</v>
       </c>
       <c r="C57" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D57" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E57" s="6">
         <v>3</v>
@@ -3581,10 +3578,10 @@
         <v>13</v>
       </c>
       <c r="C58" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D58" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E58" s="6">
         <v>3</v>
@@ -3601,10 +3598,10 @@
         <v>13</v>
       </c>
       <c r="C59" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D59" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E59" s="6">
         <v>3</v>
@@ -3621,16 +3618,16 @@
         <v>14</v>
       </c>
       <c r="C60" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D60" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E60" s="6">
         <v>6</v>
       </c>
       <c r="F60" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -3641,16 +3638,16 @@
         <v>14</v>
       </c>
       <c r="C61" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D61" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E61" s="6">
         <v>6</v>
       </c>
       <c r="F61" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -3661,16 +3658,16 @@
         <v>14</v>
       </c>
       <c r="C62" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D62" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E62" s="6">
         <v>6</v>
       </c>
       <c r="F62" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -3681,16 +3678,16 @@
         <v>14</v>
       </c>
       <c r="C63" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D63" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E63" s="6">
         <v>6</v>
       </c>
       <c r="F63" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -3701,16 +3698,16 @@
         <v>14</v>
       </c>
       <c r="C64" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D64" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E64" s="6">
         <v>6</v>
       </c>
       <c r="F64" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -3721,10 +3718,10 @@
         <v>15</v>
       </c>
       <c r="C65" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D65" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E65" s="6">
         <v>1</v>
@@ -3741,10 +3738,10 @@
         <v>15</v>
       </c>
       <c r="C66" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D66" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E66" s="6">
         <v>1</v>
@@ -3761,10 +3758,10 @@
         <v>15</v>
       </c>
       <c r="C67" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D67" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E67" s="6">
         <v>1</v>
@@ -3781,10 +3778,10 @@
         <v>15</v>
       </c>
       <c r="C68" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D68" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E68" s="6">
         <v>1</v>
@@ -3801,10 +3798,10 @@
         <v>15</v>
       </c>
       <c r="C69" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D69" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E69" s="6">
         <v>1</v>
@@ -3821,10 +3818,10 @@
         <v>16</v>
       </c>
       <c r="C70" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D70" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E70" s="6">
         <v>1</v>
@@ -3841,10 +3838,10 @@
         <v>16</v>
       </c>
       <c r="C71" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D71" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E71" s="6">
         <v>1</v>
@@ -3861,10 +3858,10 @@
         <v>16</v>
       </c>
       <c r="C72" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D72" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E72" s="6">
         <v>1</v>
@@ -3881,10 +3878,10 @@
         <v>16</v>
       </c>
       <c r="C73" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D73" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E73" s="6">
         <v>1</v>
@@ -3901,10 +3898,10 @@
         <v>16</v>
       </c>
       <c r="C74" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D74" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E74" s="6">
         <v>1</v>
@@ -3921,16 +3918,16 @@
         <v>17</v>
       </c>
       <c r="C75" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D75" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E75" s="6">
         <v>6</v>
       </c>
       <c r="F75" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -3941,16 +3938,16 @@
         <v>17</v>
       </c>
       <c r="C76" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D76" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E76" s="6">
         <v>6</v>
       </c>
       <c r="F76" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -3961,16 +3958,16 @@
         <v>17</v>
       </c>
       <c r="C77" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D77" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E77" s="6">
         <v>6</v>
       </c>
       <c r="F77" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -3981,16 +3978,16 @@
         <v>17</v>
       </c>
       <c r="C78" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D78" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E78" s="6">
         <v>6</v>
       </c>
       <c r="F78" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -4001,16 +3998,16 @@
         <v>17</v>
       </c>
       <c r="C79" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D79" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E79" s="6">
         <v>6</v>
       </c>
       <c r="F79" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -4021,10 +4018,10 @@
         <v>18</v>
       </c>
       <c r="C80" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D80" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E80" s="6">
         <v>3</v>
@@ -4041,10 +4038,10 @@
         <v>18</v>
       </c>
       <c r="C81" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D81" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E81" s="6">
         <v>3</v>
@@ -4061,10 +4058,10 @@
         <v>18</v>
       </c>
       <c r="C82" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D82" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E82" s="6">
         <v>3</v>
@@ -4081,10 +4078,10 @@
         <v>18</v>
       </c>
       <c r="C83" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D83" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E83" s="6">
         <v>3</v>
@@ -4101,10 +4098,10 @@
         <v>18</v>
       </c>
       <c r="C84" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D84" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E84" s="6">
         <v>3</v>
@@ -4121,10 +4118,10 @@
         <v>18</v>
       </c>
       <c r="C85" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D85" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E85" s="6">
         <v>3</v>
@@ -4141,10 +4138,10 @@
         <v>18</v>
       </c>
       <c r="C86" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D86" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E86" s="6">
         <v>3</v>
@@ -4161,10 +4158,10 @@
         <v>18</v>
       </c>
       <c r="C87" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D87" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E87" s="6">
         <v>3</v>
@@ -4181,10 +4178,10 @@
         <v>19</v>
       </c>
       <c r="C88" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D88" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E88" s="6">
         <v>3</v>
@@ -4201,10 +4198,10 @@
         <v>19</v>
       </c>
       <c r="C89" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D89" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E89" s="6">
         <v>3</v>
@@ -4221,10 +4218,10 @@
         <v>19</v>
       </c>
       <c r="C90" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D90" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E90" s="6">
         <v>3</v>
@@ -4241,10 +4238,10 @@
         <v>19</v>
       </c>
       <c r="C91" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D91" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E91" s="6">
         <v>3</v>
@@ -4261,10 +4258,10 @@
         <v>19</v>
       </c>
       <c r="C92" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D92" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E92" s="6">
         <v>3</v>
@@ -4281,10 +4278,10 @@
         <v>19</v>
       </c>
       <c r="C93" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D93" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E93" s="6">
         <v>3</v>
@@ -4301,10 +4298,10 @@
         <v>19</v>
       </c>
       <c r="C94" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D94" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E94" s="6">
         <v>3</v>
@@ -4321,10 +4318,10 @@
         <v>19</v>
       </c>
       <c r="C95" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D95" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E95" s="6">
         <v>3</v>
@@ -4341,10 +4338,10 @@
         <v>21</v>
       </c>
       <c r="C96" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D96" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E96" s="6">
         <v>1</v>
@@ -4361,10 +4358,10 @@
         <v>21</v>
       </c>
       <c r="C97" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D97" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E97" s="6">
         <v>1</v>
@@ -4381,10 +4378,10 @@
         <v>21</v>
       </c>
       <c r="C98" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D98" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E98" s="6">
         <v>1</v>
@@ -4401,10 +4398,10 @@
         <v>21</v>
       </c>
       <c r="C99" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D99" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E99" s="6">
         <v>1</v>
@@ -4421,10 +4418,10 @@
         <v>21</v>
       </c>
       <c r="C100" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D100" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E100" s="6">
         <v>1</v>
@@ -4441,10 +4438,10 @@
         <v>22</v>
       </c>
       <c r="C101" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D101" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E101" s="6">
         <v>3</v>
@@ -4461,10 +4458,10 @@
         <v>22</v>
       </c>
       <c r="C102" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D102" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E102" s="6">
         <v>3</v>
@@ -4481,10 +4478,10 @@
         <v>22</v>
       </c>
       <c r="C103" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D103" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E103" s="6">
         <v>3</v>
@@ -4501,10 +4498,10 @@
         <v>22</v>
       </c>
       <c r="C104" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D104" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E104" s="6">
         <v>3</v>
@@ -4521,10 +4518,10 @@
         <v>22</v>
       </c>
       <c r="C105" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D105" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E105" s="6">
         <v>3</v>
@@ -4541,16 +4538,16 @@
         <v>23</v>
       </c>
       <c r="C106" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D106" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E106" s="6">
         <v>5</v>
       </c>
       <c r="F106" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
@@ -4561,16 +4558,16 @@
         <v>23</v>
       </c>
       <c r="C107" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D107" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E107" s="6">
         <v>5</v>
       </c>
       <c r="F107" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -4581,16 +4578,16 @@
         <v>23</v>
       </c>
       <c r="C108" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D108" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E108" s="6">
         <v>5</v>
       </c>
       <c r="F108" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -4601,16 +4598,16 @@
         <v>23</v>
       </c>
       <c r="C109" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D109" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E109" s="6">
         <v>5</v>
       </c>
       <c r="F109" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -4621,16 +4618,16 @@
         <v>23</v>
       </c>
       <c r="C110" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D110" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E110" s="6">
         <v>5</v>
       </c>
       <c r="F110" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -4641,16 +4638,16 @@
         <v>24</v>
       </c>
       <c r="C111" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D111" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E111" s="6">
         <v>5</v>
       </c>
       <c r="F111" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
@@ -4661,16 +4658,16 @@
         <v>24</v>
       </c>
       <c r="C112" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D112" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E112" s="6">
         <v>5</v>
       </c>
       <c r="F112" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
@@ -4681,16 +4678,16 @@
         <v>24</v>
       </c>
       <c r="C113" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D113" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E113" s="6">
         <v>5</v>
       </c>
       <c r="F113" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
@@ -4701,16 +4698,16 @@
         <v>24</v>
       </c>
       <c r="C114" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D114" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E114" s="6">
         <v>5</v>
       </c>
       <c r="F114" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
@@ -4721,16 +4718,16 @@
         <v>24</v>
       </c>
       <c r="C115" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D115" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E115" s="6">
         <v>5</v>
       </c>
       <c r="F115" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
@@ -4741,16 +4738,16 @@
         <v>25</v>
       </c>
       <c r="C116" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D116" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E116" s="6">
         <v>5</v>
       </c>
       <c r="F116" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
@@ -4761,16 +4758,16 @@
         <v>25</v>
       </c>
       <c r="C117" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D117" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E117" s="6">
         <v>5</v>
       </c>
       <c r="F117" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -4781,16 +4778,16 @@
         <v>25</v>
       </c>
       <c r="C118" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D118" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E118" s="6">
         <v>5</v>
       </c>
       <c r="F118" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
@@ -4801,16 +4798,16 @@
         <v>25</v>
       </c>
       <c r="C119" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D119" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E119" s="6">
         <v>5</v>
       </c>
       <c r="F119" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
@@ -4821,16 +4818,16 @@
         <v>25</v>
       </c>
       <c r="C120" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D120" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E120" s="6">
         <v>5</v>
       </c>
       <c r="F120" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -4841,10 +4838,10 @@
         <v>26</v>
       </c>
       <c r="C121" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D121" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E121" s="6">
         <v>4</v>
@@ -4861,10 +4858,10 @@
         <v>26</v>
       </c>
       <c r="C122" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D122" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E122" s="6">
         <v>4</v>
@@ -4881,10 +4878,10 @@
         <v>26</v>
       </c>
       <c r="C123" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D123" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E123" s="6">
         <v>4</v>
@@ -4901,10 +4898,10 @@
         <v>26</v>
       </c>
       <c r="C124" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D124" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E124" s="6">
         <v>4</v>
@@ -4921,10 +4918,10 @@
         <v>26</v>
       </c>
       <c r="C125" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D125" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E125" s="6">
         <v>4</v>
@@ -4941,10 +4938,10 @@
         <v>27</v>
       </c>
       <c r="C126" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D126" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E126" s="6">
         <v>3</v>
@@ -4955,16 +4952,16 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B127" t="s">
         <v>27</v>
       </c>
       <c r="C127" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D127" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E127" s="6">
         <v>3</v>
@@ -4975,16 +4972,16 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B128" t="s">
         <v>27</v>
       </c>
       <c r="C128" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D128" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E128" s="6">
         <v>3</v>
@@ -4995,16 +4992,16 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B129" t="s">
         <v>28</v>
       </c>
       <c r="C129" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D129" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E129" s="6">
         <v>3</v>
@@ -5015,16 +5012,16 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B130" t="s">
         <v>28</v>
       </c>
       <c r="C130" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D130" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E130" s="6">
         <v>3</v>
@@ -5035,16 +5032,16 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B131" t="s">
         <v>28</v>
       </c>
       <c r="C131" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D131" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E131" s="6">
         <v>3</v>
@@ -5055,16 +5052,16 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B132" t="s">
         <v>29</v>
       </c>
       <c r="C132" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D132" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E132" s="6">
         <v>3</v>
@@ -5075,16 +5072,16 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B133" t="s">
         <v>29</v>
       </c>
       <c r="C133" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D133" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E133" s="6">
         <v>3</v>
@@ -5095,16 +5092,16 @@
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B134" t="s">
         <v>29</v>
       </c>
       <c r="C134" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D134" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E134" s="6">
         <v>3</v>
@@ -5115,16 +5112,16 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B135" t="s">
         <v>30</v>
       </c>
       <c r="C135" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D135" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E135" s="6">
         <v>3</v>
@@ -5135,16 +5132,16 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B136" t="s">
         <v>30</v>
       </c>
       <c r="C136" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D136" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E136" s="6">
         <v>3</v>
@@ -5155,16 +5152,16 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B137" t="s">
         <v>30</v>
       </c>
       <c r="C137" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D137" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E137" s="6">
         <v>3</v>
@@ -5175,16 +5172,16 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B138" t="s">
         <v>30</v>
       </c>
       <c r="C138" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D138" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E138" s="6">
         <v>3</v>
@@ -5195,16 +5192,16 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B139" t="s">
         <v>30</v>
       </c>
       <c r="C139" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D139" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E139" s="6">
         <v>3</v>
@@ -5215,16 +5212,16 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B140" t="s">
         <v>31</v>
       </c>
       <c r="C140" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D140" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E140" s="6">
         <v>3</v>
@@ -5235,16 +5232,16 @@
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B141" t="s">
         <v>31</v>
       </c>
       <c r="C141" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D141" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E141" s="6">
         <v>3</v>
@@ -5255,16 +5252,16 @@
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B142" t="s">
         <v>31</v>
       </c>
       <c r="C142" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D142" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E142" s="6">
         <v>3</v>
@@ -5275,16 +5272,16 @@
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B143" t="s">
         <v>31</v>
       </c>
       <c r="C143" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D143" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E143" s="6">
         <v>3</v>
@@ -5295,16 +5292,16 @@
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B144" t="s">
         <v>31</v>
       </c>
       <c r="C144" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D144" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E144" s="6">
         <v>3</v>
@@ -5315,16 +5312,16 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B145" t="s">
         <v>31</v>
       </c>
       <c r="C145" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D145" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E145" s="6">
         <v>3</v>
@@ -5335,16 +5332,16 @@
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B146" t="s">
         <v>31</v>
       </c>
       <c r="C146" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D146" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E146" s="6">
         <v>3</v>
@@ -5355,16 +5352,16 @@
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B147" t="s">
         <v>31</v>
       </c>
       <c r="C147" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D147" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E147" s="6">
         <v>3</v>
@@ -5375,16 +5372,16 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B148" t="s">
         <v>32</v>
       </c>
       <c r="C148" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D148" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E148" s="6">
         <v>3</v>
@@ -5395,16 +5392,16 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B149" t="s">
         <v>32</v>
       </c>
       <c r="C149" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D149" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E149" s="6">
         <v>3</v>
@@ -5415,16 +5412,16 @@
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B150" t="s">
         <v>32</v>
       </c>
       <c r="C150" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D150" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E150" s="6">
         <v>3</v>
@@ -5435,16 +5432,16 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B151" t="s">
         <v>32</v>
       </c>
       <c r="C151" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D151" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E151" s="6">
         <v>3</v>
@@ -5455,16 +5452,16 @@
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B152" t="s">
         <v>32</v>
       </c>
       <c r="C152" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D152" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E152" s="6">
         <v>3</v>
@@ -5475,16 +5472,16 @@
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B153" t="s">
         <v>33</v>
       </c>
       <c r="C153" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D153" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E153" s="6">
         <v>3</v>
@@ -5495,16 +5492,16 @@
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B154" t="s">
         <v>33</v>
       </c>
       <c r="C154" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D154" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E154" s="6">
         <v>3</v>
@@ -5515,16 +5512,16 @@
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B155" t="s">
         <v>33</v>
       </c>
       <c r="C155" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D155" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E155" s="6">
         <v>3</v>
@@ -5535,16 +5532,16 @@
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B156" t="s">
         <v>33</v>
       </c>
       <c r="C156" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D156" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E156" s="6">
         <v>3</v>
@@ -5555,16 +5552,16 @@
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B157" t="s">
         <v>33</v>
       </c>
       <c r="C157" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D157" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E157" s="6">
         <v>3</v>
@@ -5575,16 +5572,16 @@
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B158" t="s">
         <v>34</v>
       </c>
       <c r="C158" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D158" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E158" s="6">
         <v>4</v>
@@ -5595,16 +5592,16 @@
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B159" t="s">
         <v>34</v>
       </c>
       <c r="C159" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D159" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E159" s="6">
         <v>4</v>
@@ -5615,16 +5612,16 @@
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B160" t="s">
         <v>34</v>
       </c>
       <c r="C160" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D160" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E160" s="6">
         <v>4</v>
@@ -5635,16 +5632,16 @@
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B161" t="s">
         <v>34</v>
       </c>
       <c r="C161" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D161" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E161" s="6">
         <v>4</v>
@@ -5655,16 +5652,16 @@
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B162" t="s">
         <v>34</v>
       </c>
       <c r="C162" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D162" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E162" s="6">
         <v>4</v>
@@ -5675,216 +5672,216 @@
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B163" t="s">
         <v>35</v>
       </c>
       <c r="C163" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D163" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E163" s="6">
         <v>5</v>
       </c>
       <c r="F163" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B164" t="s">
         <v>35</v>
       </c>
       <c r="C164" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D164" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E164" s="6">
         <v>5</v>
       </c>
       <c r="F164" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B165" t="s">
         <v>35</v>
       </c>
       <c r="C165" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D165" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E165" s="6">
         <v>5</v>
       </c>
       <c r="F165" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B166" t="s">
         <v>35</v>
       </c>
       <c r="C166" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D166" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E166" s="6">
         <v>5</v>
       </c>
       <c r="F166" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B167" t="s">
         <v>35</v>
       </c>
       <c r="C167" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D167" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E167" s="6">
         <v>5</v>
       </c>
       <c r="F167" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B168" t="s">
         <v>36</v>
       </c>
       <c r="C168" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D168" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E168" s="6">
         <v>6</v>
       </c>
       <c r="F168" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B169" t="s">
         <v>36</v>
       </c>
       <c r="C169" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D169" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E169" s="6">
         <v>6</v>
       </c>
       <c r="F169" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B170" t="s">
         <v>36</v>
       </c>
       <c r="C170" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D170" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E170" s="6">
         <v>6</v>
       </c>
       <c r="F170" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B171" t="s">
         <v>36</v>
       </c>
       <c r="C171" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D171" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E171" s="6">
         <v>6</v>
       </c>
       <c r="F171" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B172" t="s">
         <v>36</v>
       </c>
       <c r="C172" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D172" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E172" s="6">
         <v>6</v>
       </c>
       <c r="F172" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B173" t="s">
         <v>37</v>
       </c>
       <c r="C173" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D173" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E173" s="6">
         <v>3</v>
@@ -5895,16 +5892,16 @@
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B174" t="s">
         <v>37</v>
       </c>
       <c r="C174" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D174" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E174" s="6">
         <v>3</v>
@@ -5915,16 +5912,16 @@
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B175" t="s">
         <v>38</v>
       </c>
       <c r="C175" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D175" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E175" s="6">
         <v>4</v>
@@ -5935,16 +5932,16 @@
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B176" t="s">
         <v>38</v>
       </c>
       <c r="C176" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D176" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E176" s="6">
         <v>4</v>
@@ -5955,16 +5952,16 @@
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B177" t="s">
         <v>38</v>
       </c>
       <c r="C177" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D177" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E177" s="6">
         <v>4</v>
@@ -5975,16 +5972,16 @@
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B178" t="s">
         <v>38</v>
       </c>
       <c r="C178" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D178" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E178" s="6">
         <v>4</v>
@@ -5995,16 +5992,16 @@
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B179" t="s">
         <v>38</v>
       </c>
       <c r="C179" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D179" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E179" s="6">
         <v>4</v>
@@ -6033,22 +6030,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>141</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -6068,7 +6065,7 @@
         <v>20</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -6088,7 +6085,7 @@
         <v>20</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -6108,7 +6105,7 @@
         <v>40</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -6128,7 +6125,7 @@
         <v>40</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -6146,7 +6143,7 @@
         <v>20</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -6166,7 +6163,7 @@
         <v>40</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -6186,7 +6183,7 @@
         <v>40</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -6206,7 +6203,7 @@
         <v>40</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -6223,7 +6220,7 @@
         <v>40</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -6243,7 +6240,7 @@
         <v>40</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -6263,7 +6260,7 @@
         <v>40</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -6283,7 +6280,7 @@
         <v>40</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -6303,7 +6300,7 @@
         <v>20</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -6323,7 +6320,7 @@
         <v>40</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -6343,7 +6340,7 @@
         <v>40</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -6363,7 +6360,7 @@
         <v>40</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -6381,7 +6378,7 @@
         <v>20</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -6401,7 +6398,7 @@
         <v>40</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -6421,7 +6418,7 @@
         <v>40</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -6441,7 +6438,7 @@
         <v>40</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -6458,7 +6455,7 @@
         <v>40</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -6478,7 +6475,7 @@
         <v>40</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -6498,7 +6495,7 @@
         <v>40</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -6518,7 +6515,7 @@
         <v>40</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -6538,7 +6535,7 @@
         <v>20</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -6558,7 +6555,7 @@
         <v>40</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -6578,7 +6575,7 @@
         <v>40</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -6598,7 +6595,7 @@
         <v>40</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -6616,7 +6613,7 @@
         <v>20</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -6636,7 +6633,7 @@
         <v>40</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -6656,7 +6653,7 @@
         <v>40</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -6676,7 +6673,7 @@
         <v>40</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -6693,7 +6690,7 @@
         <v>40</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -6713,7 +6710,7 @@
         <v>40</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -6733,7 +6730,7 @@
         <v>40</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -6753,7 +6750,7 @@
         <v>40</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -6773,7 +6770,7 @@
         <v>20</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -6793,7 +6790,7 @@
         <v>40</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -6813,7 +6810,7 @@
         <v>40</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -6833,7 +6830,7 @@
         <v>40</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -6851,7 +6848,7 @@
         <v>20</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -6871,7 +6868,7 @@
         <v>40</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -6891,7 +6888,7 @@
         <v>40</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -6911,7 +6908,7 @@
         <v>40</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -6928,7 +6925,7 @@
         <v>40</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -6948,7 +6945,7 @@
         <v>40</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -6968,7 +6965,7 @@
         <v>40</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -6988,7 +6985,7 @@
         <v>40</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -7008,7 +7005,7 @@
         <v>40</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -7028,7 +7025,7 @@
         <v>30</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -7048,7 +7045,7 @@
         <v>30</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -7068,7 +7065,7 @@
         <v>30</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -7086,7 +7083,7 @@
         <v>20</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -7106,7 +7103,7 @@
         <v>30</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -7126,7 +7123,7 @@
         <v>30</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -7146,7 +7143,7 @@
         <v>30</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>

--- a/data/database_scheduler.xlsx
+++ b/data/database_scheduler.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Mersi\BZ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FE9AB7B-A25D-4D67-91B7-1CE9A235834F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD873CAC-1F22-48F9-AB3A-9D7374AB517C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{AE6D36E3-81A9-434A-AA02-B2E060EB1A89}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1075" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1119" uniqueCount="150">
   <si>
     <t>Nama Guru</t>
   </si>
@@ -2377,7 +2377,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E6B6589-81EB-464C-9D2E-94A0AC6F84FB}">
-  <dimension ref="A1:L179"/>
+  <dimension ref="A1:L190"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.5703125" customWidth="1"/>
@@ -3724,10 +3724,10 @@
         <v>120</v>
       </c>
       <c r="E65" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F65" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -3744,10 +3744,10 @@
         <v>128</v>
       </c>
       <c r="E66" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F66" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -3764,10 +3764,10 @@
         <v>129</v>
       </c>
       <c r="E67" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F67" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -3784,10 +3784,10 @@
         <v>130</v>
       </c>
       <c r="E68" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F68" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -3804,10 +3804,10 @@
         <v>131</v>
       </c>
       <c r="E69" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F69" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -3824,10 +3824,10 @@
         <v>117</v>
       </c>
       <c r="E70" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F70" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -3844,10 +3844,10 @@
         <v>118</v>
       </c>
       <c r="E71" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F71" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -3864,10 +3864,10 @@
         <v>121</v>
       </c>
       <c r="E72" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F72" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -3884,10 +3884,10 @@
         <v>122</v>
       </c>
       <c r="E73" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F73" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -3904,10 +3904,10 @@
         <v>123</v>
       </c>
       <c r="E74" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F74" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -4344,10 +4344,10 @@
         <v>119</v>
       </c>
       <c r="E96" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F96" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -4364,10 +4364,10 @@
         <v>124</v>
       </c>
       <c r="E97" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F97" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -4384,10 +4384,10 @@
         <v>125</v>
       </c>
       <c r="E98" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F98" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -4404,10 +4404,10 @@
         <v>126</v>
       </c>
       <c r="E99" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F99" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -4424,10 +4424,10 @@
         <v>127</v>
       </c>
       <c r="E100" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F100" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -4932,242 +4932,242 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B126" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C126" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D126" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="E126" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F126" s="6">
-        <v>3</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B127" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C127" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D127" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E127" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F127" s="6">
-        <v>3</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B128" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C128" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D128" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="E128" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F128" s="6">
-        <v>3</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B129" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C129" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D129" t="s">
         <v>117</v>
       </c>
       <c r="E129" s="6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F129" s="6">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B130" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C130" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D130" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="E130" s="6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F130" s="6">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B131" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C131" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D131" t="s">
         <v>120</v>
       </c>
       <c r="E131" s="6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F131" s="6">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B132" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C132" t="s">
-        <v>149</v>
+        <v>111</v>
       </c>
       <c r="D132" t="s">
         <v>117</v>
       </c>
       <c r="E132" s="6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F132" s="6">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B133" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C133" t="s">
-        <v>149</v>
+        <v>111</v>
       </c>
       <c r="D133" t="s">
         <v>119</v>
       </c>
       <c r="E133" s="6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F133" s="6">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B134" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C134" t="s">
-        <v>149</v>
+        <v>111</v>
       </c>
       <c r="D134" t="s">
         <v>120</v>
       </c>
       <c r="E134" s="6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F134" s="6">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B135" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C135" t="s">
-        <v>107</v>
+        <v>149</v>
       </c>
       <c r="D135" t="s">
         <v>117</v>
       </c>
       <c r="E135" s="6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F135" s="6">
-        <v>2.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B136" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C136" t="s">
-        <v>107</v>
+        <v>149</v>
       </c>
       <c r="D136" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E136" s="6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F136" s="6">
-        <v>2.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B137" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C137" t="s">
-        <v>107</v>
+        <v>149</v>
       </c>
       <c r="D137" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E137" s="6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F137" s="6">
-        <v>2.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
@@ -5181,7 +5181,7 @@
         <v>107</v>
       </c>
       <c r="D138" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="E138" s="6">
         <v>3</v>
@@ -5201,7 +5201,7 @@
         <v>107</v>
       </c>
       <c r="D139" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="E139" s="6">
         <v>3</v>
@@ -5212,102 +5212,102 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B140" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C140" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="D140" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E140" s="6">
         <v>3</v>
       </c>
       <c r="F140" s="6">
-        <v>3</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B141" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C141" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="D141" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="E141" s="6">
         <v>3</v>
       </c>
       <c r="F141" s="6">
-        <v>3</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B142" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C142" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="D142" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E142" s="6">
         <v>3</v>
       </c>
       <c r="F142" s="6">
-        <v>3</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B143" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C143" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="D143" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E143" s="6">
         <v>3</v>
       </c>
       <c r="F143" s="6">
-        <v>3</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B144" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C144" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="D144" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="E144" s="6">
         <v>3</v>
       </c>
       <c r="F144" s="6">
-        <v>3</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
@@ -5318,10 +5318,10 @@
         <v>31</v>
       </c>
       <c r="C145" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="D145" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="E145" s="6">
         <v>3</v>
@@ -5338,10 +5338,10 @@
         <v>31</v>
       </c>
       <c r="C146" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="D146" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="E146" s="6">
         <v>3</v>
@@ -5358,10 +5358,10 @@
         <v>31</v>
       </c>
       <c r="C147" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="D147" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="E147" s="6">
         <v>3</v>
@@ -5372,13 +5372,13 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B148" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C148" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="D148" t="s">
         <v>122</v>
@@ -5392,13 +5392,13 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B149" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C149" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="D149" t="s">
         <v>123</v>
@@ -5412,16 +5412,16 @@
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B150" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C150" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="D150" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="E150" s="6">
         <v>3</v>
@@ -5432,16 +5432,16 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B151" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C151" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="D151" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E151" s="6">
         <v>3</v>
@@ -5452,16 +5452,16 @@
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B152" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C152" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="D152" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E152" s="6">
         <v>3</v>
@@ -5472,16 +5472,16 @@
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B153" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C153" t="s">
-        <v>87</v>
+        <v>106</v>
       </c>
       <c r="D153" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="E153" s="6">
         <v>3</v>
@@ -5492,16 +5492,16 @@
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B154" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C154" t="s">
-        <v>87</v>
+        <v>106</v>
       </c>
       <c r="D154" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="E154" s="6">
         <v>3</v>
@@ -5512,16 +5512,16 @@
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B155" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C155" t="s">
-        <v>87</v>
+        <v>106</v>
       </c>
       <c r="D155" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E155" s="6">
         <v>3</v>
@@ -5532,16 +5532,16 @@
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B156" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C156" t="s">
-        <v>87</v>
+        <v>106</v>
       </c>
       <c r="D156" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="E156" s="6">
         <v>3</v>
@@ -5552,16 +5552,16 @@
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B157" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C157" t="s">
-        <v>87</v>
+        <v>106</v>
       </c>
       <c r="D157" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="E157" s="6">
         <v>3</v>
@@ -5572,441 +5572,661 @@
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B158" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C158" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D158" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="E158" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F158" s="6">
-        <v>2.2000000000000002</v>
+        <v>3</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B159" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C159" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D159" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="E159" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F159" s="6">
-        <v>2.2000000000000002</v>
+        <v>3</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B160" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C160" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="D160" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="E160" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F160" s="6">
-        <v>2.2000000000000002</v>
+        <v>3</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B161" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C161" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="D161" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E161" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F161" s="6">
-        <v>2.2000000000000002</v>
+        <v>3</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B162" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C162" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="D162" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E162" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F162" s="6">
-        <v>2.2000000000000002</v>
+        <v>3</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B163" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C163" t="s">
-        <v>108</v>
+        <v>87</v>
       </c>
       <c r="D163" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E163" s="6">
-        <v>5</v>
-      </c>
-      <c r="F163" s="6" t="s">
-        <v>134</v>
+        <v>3</v>
+      </c>
+      <c r="F163" s="6">
+        <v>3</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B164" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C164" t="s">
-        <v>108</v>
+        <v>87</v>
       </c>
       <c r="D164" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E164" s="6">
-        <v>5</v>
-      </c>
-      <c r="F164" s="6" t="s">
-        <v>134</v>
+        <v>3</v>
+      </c>
+      <c r="F164" s="6">
+        <v>3</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B165" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C165" t="s">
-        <v>108</v>
+        <v>87</v>
       </c>
       <c r="D165" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E165" s="6">
-        <v>5</v>
-      </c>
-      <c r="F165" s="6" t="s">
-        <v>134</v>
+        <v>3</v>
+      </c>
+      <c r="F165" s="6">
+        <v>3</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B166" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C166" t="s">
-        <v>108</v>
+        <v>87</v>
       </c>
       <c r="D166" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E166" s="6">
-        <v>5</v>
-      </c>
-      <c r="F166" s="6" t="s">
-        <v>134</v>
+        <v>3</v>
+      </c>
+      <c r="F166" s="6">
+        <v>3</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B167" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C167" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D167" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="E167" s="6">
-        <v>5</v>
-      </c>
-      <c r="F167" s="6" t="s">
-        <v>134</v>
+        <v>4</v>
+      </c>
+      <c r="F167" s="6">
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B168" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C168" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="D168" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E168" s="6">
-        <v>6</v>
-      </c>
-      <c r="F168" s="6" t="s">
-        <v>135</v>
+        <v>4</v>
+      </c>
+      <c r="F168" s="6">
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B169" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C169" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="D169" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E169" s="6">
-        <v>6</v>
-      </c>
-      <c r="F169" s="6" t="s">
-        <v>135</v>
+        <v>4</v>
+      </c>
+      <c r="F169" s="6">
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B170" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C170" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="D170" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="E170" s="6">
-        <v>6</v>
-      </c>
-      <c r="F170" s="6" t="s">
-        <v>135</v>
+        <v>4</v>
+      </c>
+      <c r="F170" s="6">
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B171" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C171" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="D171" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E171" s="6">
-        <v>6</v>
-      </c>
-      <c r="F171" s="6" t="s">
-        <v>135</v>
+        <v>4</v>
+      </c>
+      <c r="F171" s="6">
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B172" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C172" t="s">
-        <v>85</v>
+        <v>108</v>
       </c>
       <c r="D172" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="E172" s="6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F172" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B173" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C173" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="D173" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="E173" s="6">
-        <v>3</v>
-      </c>
-      <c r="F173" s="6">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="F173" s="6" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B174" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C174" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="D174" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E174" s="6">
-        <v>3</v>
-      </c>
-      <c r="F174" s="6">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="F174" s="6" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B175" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C175" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D175" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="E175" s="6">
-        <v>4</v>
-      </c>
-      <c r="F175" s="6">
-        <v>2.2000000000000002</v>
+        <v>5</v>
+      </c>
+      <c r="F175" s="6" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B176" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C176" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D176" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="E176" s="6">
-        <v>4</v>
-      </c>
-      <c r="F176" s="6">
-        <v>2.2000000000000002</v>
+        <v>5</v>
+      </c>
+      <c r="F176" s="6" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B177" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C177" t="s">
-        <v>109</v>
+        <v>85</v>
       </c>
       <c r="D177" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E177" s="6">
-        <v>4</v>
-      </c>
-      <c r="F177" s="6">
-        <v>2.2000000000000002</v>
+        <v>6</v>
+      </c>
+      <c r="F177" s="6" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B178" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C178" t="s">
-        <v>109</v>
+        <v>85</v>
       </c>
       <c r="D178" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E178" s="6">
-        <v>4</v>
-      </c>
-      <c r="F178" s="6">
-        <v>2.2000000000000002</v>
+        <v>6</v>
+      </c>
+      <c r="F178" s="6" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B179" t="s">
+        <v>36</v>
+      </c>
+      <c r="C179" t="s">
+        <v>85</v>
+      </c>
+      <c r="D179" t="s">
+        <v>125</v>
+      </c>
+      <c r="E179" s="6">
+        <v>6</v>
+      </c>
+      <c r="F179" s="6" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A180" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B180" t="s">
+        <v>36</v>
+      </c>
+      <c r="C180" t="s">
+        <v>85</v>
+      </c>
+      <c r="D180" t="s">
+        <v>126</v>
+      </c>
+      <c r="E180" s="6">
+        <v>6</v>
+      </c>
+      <c r="F180" s="6" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A181" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B181" t="s">
+        <v>36</v>
+      </c>
+      <c r="C181" t="s">
+        <v>85</v>
+      </c>
+      <c r="D181" t="s">
+        <v>127</v>
+      </c>
+      <c r="E181" s="6">
+        <v>6</v>
+      </c>
+      <c r="F181" s="6" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A182" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B182" t="s">
+        <v>37</v>
+      </c>
+      <c r="C182" t="s">
+        <v>102</v>
+      </c>
+      <c r="D182" t="s">
+        <v>119</v>
+      </c>
+      <c r="E182" s="6">
+        <v>3</v>
+      </c>
+      <c r="F182" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A183" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B183" t="s">
+        <v>37</v>
+      </c>
+      <c r="C183" t="s">
+        <v>102</v>
+      </c>
+      <c r="D183" t="s">
+        <v>124</v>
+      </c>
+      <c r="E183" s="6">
+        <v>3</v>
+      </c>
+      <c r="F183" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A184" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="B179" t="s">
+      <c r="B184" t="s">
         <v>38</v>
       </c>
-      <c r="C179" t="s">
+      <c r="C184" t="s">
         <v>109</v>
       </c>
-      <c r="D179" t="s">
+      <c r="D184" t="s">
+        <v>117</v>
+      </c>
+      <c r="E184" s="6">
+        <v>4</v>
+      </c>
+      <c r="F184" s="6">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A185" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B185" t="s">
+        <v>38</v>
+      </c>
+      <c r="C185" t="s">
+        <v>109</v>
+      </c>
+      <c r="D185" t="s">
+        <v>118</v>
+      </c>
+      <c r="E185" s="6">
+        <v>4</v>
+      </c>
+      <c r="F185" s="6">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A186" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B186" t="s">
+        <v>38</v>
+      </c>
+      <c r="C186" t="s">
+        <v>109</v>
+      </c>
+      <c r="D186" t="s">
+        <v>121</v>
+      </c>
+      <c r="E186" s="6">
+        <v>4</v>
+      </c>
+      <c r="F186" s="6">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A187" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B187" t="s">
+        <v>38</v>
+      </c>
+      <c r="C187" t="s">
+        <v>109</v>
+      </c>
+      <c r="D187" t="s">
+        <v>122</v>
+      </c>
+      <c r="E187" s="6">
+        <v>4</v>
+      </c>
+      <c r="F187" s="6">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A188" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B188" t="s">
+        <v>38</v>
+      </c>
+      <c r="C188" t="s">
+        <v>109</v>
+      </c>
+      <c r="D188" t="s">
         <v>123</v>
       </c>
-      <c r="E179" s="6">
+      <c r="E188" s="6">
         <v>4</v>
       </c>
-      <c r="F179" s="6">
+      <c r="F188" s="6">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A189" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B189" t="s">
+        <v>38</v>
+      </c>
+      <c r="C189" t="s">
+        <v>109</v>
+      </c>
+      <c r="D189" t="s">
+        <v>119</v>
+      </c>
+      <c r="E189" s="6">
+        <v>4</v>
+      </c>
+      <c r="F189" s="6">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A190" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B190" t="s">
+        <v>38</v>
+      </c>
+      <c r="C190" t="s">
+        <v>109</v>
+      </c>
+      <c r="D190" t="s">
+        <v>124</v>
+      </c>
+      <c r="E190" s="6">
+        <v>4</v>
+      </c>
+      <c r="F190" s="6">
         <v>2.2000000000000002</v>
       </c>
     </row>

--- a/data/database_scheduler.xlsx
+++ b/data/database_scheduler.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Mersi\BZ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD873CAC-1F22-48F9-AB3A-9D7374AB517C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBDBD0AA-C0B4-4D72-B3BC-7DF6A6C1CE2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{AE6D36E3-81A9-434A-AA02-B2E060EB1A89}"/>
   </bookViews>

--- a/data/database_scheduler.xlsx
+++ b/data/database_scheduler.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Mersi\BZ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBDBD0AA-C0B4-4D72-B3BC-7DF6A6C1CE2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5479B5AC-D950-4C6F-A1E6-D5D1B57AAD4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{AE6D36E3-81A9-434A-AA02-B2E060EB1A89}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{AE6D36E3-81A9-434A-AA02-B2E060EB1A89}"/>
   </bookViews>
   <sheets>
     <sheet name="Guru" sheetId="2" r:id="rId1"/>
@@ -1496,7 +1496,7 @@
         <v>6</v>
       </c>
       <c r="E9" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -1513,7 +1513,7 @@
         <v>8</v>
       </c>
       <c r="E10" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -1547,7 +1547,7 @@
         <v>4</v>
       </c>
       <c r="E12" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -1564,7 +1564,7 @@
         <v>4</v>
       </c>
       <c r="E13" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -1632,7 +1632,7 @@
         <v>4</v>
       </c>
       <c r="E17" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -1717,7 +1717,7 @@
         <v>4</v>
       </c>
       <c r="E22" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -1734,7 +1734,7 @@
         <v>4</v>
       </c>
       <c r="E23" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -1751,7 +1751,7 @@
         <v>2</v>
       </c>
       <c r="E24" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -1768,7 +1768,7 @@
         <v>2</v>
       </c>
       <c r="E25" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -1785,7 +1785,7 @@
         <v>20</v>
       </c>
       <c r="E26" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -1802,7 +1802,7 @@
         <v>20</v>
       </c>
       <c r="E27" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -1819,7 +1819,7 @@
         <v>6</v>
       </c>
       <c r="E28" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -1938,7 +1938,7 @@
         <v>4</v>
       </c>
       <c r="E35" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -2144,7 +2144,7 @@
         <v>105</v>
       </c>
       <c r="C17" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">

--- a/data/database_scheduler.xlsx
+++ b/data/database_scheduler.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Mersi\BZ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5479B5AC-D950-4C6F-A1E6-D5D1B57AAD4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9EA0C3B-85B1-42F4-ADE2-98953E7202BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{AE6D36E3-81A9-434A-AA02-B2E060EB1A89}"/>
   </bookViews>
